--- a/docs/brake_balance.xlsx
+++ b/docs/brake_balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E55BF8-CA84-4CBE-86AF-5821BD341C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3B56B9-BA01-482A-B0FA-8B83562A53B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,17 +35,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>Astral · Brake balance</t>
   </si>
   <si>
-    <t>前轴制动扭矩占比 · 行 = 前主缸 MC，列 = 后主缸 MC</t>
-  </si>
-  <si>
-    <t>Front brake share</t>
-  </si>
-  <si>
     <t>Setup</t>
   </si>
   <si>
@@ -73,9 +67,6 @@
     <t>Rear pad</t>
   </si>
   <si>
-    <t>黄色可编辑 · Balance bar 40–60%</t>
-  </si>
-  <si>
     <t>固定色阶</t>
   </si>
   <si>
@@ -88,18 +79,9 @@
     <t>偏前</t>
   </si>
   <si>
-    <t>每格 = 前轴扭矩 /（前轴扭矩 + 后轴扭矩）；后轴占比 = 100% − 该值。</t>
-  </si>
-  <si>
-    <t>按当前 JBeam 基础参数计算，不包含热衰减、轮胎抓地或载荷转移。</t>
-  </si>
-  <si>
     <t>Astral · Brake parameters</t>
   </si>
   <si>
-    <t>黄色数值为模型标定；前后轴可分别修改。</t>
-  </si>
-  <si>
     <t>Brake disc constants</t>
   </si>
   <si>
@@ -130,49 +112,13 @@
     <t>Type-B</t>
   </si>
   <si>
-    <t>数据来源</t>
-  </si>
-  <si>
     <t>Master cylinder multipliers</t>
   </si>
   <si>
-    <t>Astral_brakes.jbeam</t>
-  </si>
-  <si>
     <t>MC (mm)</t>
   </si>
   <si>
-    <t>Astral_brakeaux_F.jbeam</t>
-  </si>
-  <si>
-    <t>Astral_brakeaux_R.jbeam</t>
-  </si>
-  <si>
-    <t>Calculation</t>
-  </si>
-  <si>
-    <t>前轴权重 F = 前盘 K × 前 MC 倍率 × 前片倍率 × Balance bar。</t>
-  </si>
-  <si>
-    <t>后轴权重 R = 后盘 K × 后 MC 倍率 × 后片倍率 × (1 − Balance bar)。</t>
-  </si>
-  <si>
-    <t>前轴占比 = F / (F + R)。共同 maxPressure、相同输入映射及每轴两个车轮的倍数约去。</t>
-  </si>
-  <si>
-    <t>仅计算脚刹；不含手刹及未安装前刹车时的后轴备用公式。</t>
-  </si>
-  <si>
-    <t>常数采用 JBeam 当前取整值；MC 倍率直接沿用代码，不按直径平方重新推算。</t>
-  </si>
-  <si>
-    <t>Excel 标定不会自动写回 JBeam。来源快照：2026-10-05。</t>
-  </si>
-  <si>
     <t>Astral · Brake calculations</t>
-  </si>
-  <si>
-    <t>选择器来自 Balance Map；九种 MC 组合直接计算，统一踏板力度倍率已约去。</t>
   </si>
   <si>
     <t>Selected setup</t>
@@ -227,7 +173,7 @@
     <numFmt numFmtId="178" formatCode="0&quot; mm&quot;"/>
     <numFmt numFmtId="179" formatCode="0.000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,50 +181,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF283C50"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FF283C50"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF667B91"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF283C50"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <color rgb="FF283C50"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF195DB1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF667B91"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
     </font>
@@ -293,8 +195,142 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667B91"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,12 +344,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF31475E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE9EEF3"/>
+        <fgColor rgb="FFF5F7FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -321,8 +362,113 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -345,87 +491,285 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="9" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="12" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="13" fillId="12" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="15" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="18" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="19" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="21" fillId="20" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="1" fontId="22" fillId="21" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="2" fontId="23" fillId="22" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="2" fontId="24" fillId="23" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="179" fontId="25" fillId="24" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
+    <xf numFmtId="179" fontId="26" fillId="25" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
+    <xf numFmtId="10" fontId="27" fillId="26" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="28" fillId="27" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -643,21 +987,21 @@
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="3" customWidth="1"/>
-    <col min="10" max="10" width="29.08203125" customWidth="1"/>
-    <col min="11" max="11" width="30.5" customWidth="1"/>
+    <col min="2" max="2" width="12.08203125" customWidth="1"/>
+    <col min="3" max="6" width="17.58203125" customWidth="1"/>
+    <col min="7" max="7" width="4" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="3" customWidth="1"/>
+    <col min="11" max="11" width="29.08203125" customWidth="1"/>
+    <col min="12" max="12" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -667,34 +1011,27 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="1"/>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -704,244 +1041,227 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="28"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="21" t="s">
+      <c r="B6" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0.52</v>
-      </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="D6" s="8">
         <f>Parameters!B15</f>
         <v>17.420000000000002</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E6" s="10">
         <f>Parameters!B16</f>
         <v>19</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F6" s="8">
         <f>Parameters!B17</f>
         <v>21.38</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="7">
-        <v>355</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="3">
+      <c r="G6" s="1"/>
+      <c r="H6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.52</v>
+      </c>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="8">
         <f>Parameters!B15</f>
         <v>17.420000000000002</v>
       </c>
-      <c r="C8" s="4">
+      <c r="D7" s="9">
         <f>Calculations!H13</f>
         <v>0.52000000000000013</v>
       </c>
-      <c r="D8" s="4">
+      <c r="E7" s="9">
         <f>Calculations!H14</f>
         <v>0.5631598107025847</v>
       </c>
-      <c r="E8" s="4">
+      <c r="F7" s="9">
         <f>Calculations!H15</f>
         <v>0.62004008016032064</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="7">
+      <c r="G7" s="1"/>
+      <c r="H7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="7">
         <v>355</v>
       </c>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="3">
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="10">
         <f>Parameters!B16</f>
         <v>19</v>
       </c>
-      <c r="C9" s="4">
+      <c r="D8" s="9">
         <f>Calculations!H16</f>
         <v>0.47653958944281533</v>
       </c>
-      <c r="D9" s="4">
+      <c r="E8" s="9">
         <f>Calculations!H17</f>
         <v>0.52</v>
       </c>
-      <c r="E9" s="4">
+      <c r="F8" s="9">
         <f>Calculations!H18</f>
         <v>0.57829181494661919</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3">
+      <c r="G8" s="1"/>
+      <c r="H8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="7">
+        <v>355</v>
+      </c>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="8">
         <f>Parameters!B17</f>
         <v>21.38</v>
       </c>
-      <c r="C10" s="4">
+      <c r="D9" s="9">
         <f>Calculations!H19</f>
         <v>0.4183299389002037</v>
       </c>
-      <c r="D10" s="4">
+      <c r="E9" s="9">
         <f>Calculations!H20</f>
         <v>0.46115850920520884</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F9" s="9">
         <f>Calculations!H21</f>
         <v>0.52</v>
       </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G10" s="1"/>
+      <c r="H10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="16"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="C12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0.7</v>
+      </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="8">
-        <v>0.3</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -951,8 +1271,9 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -962,31 +1283,16 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+      <c r="J19" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C6:E6"/>
+  <mergeCells count="3">
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="H5:I5"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
-  <conditionalFormatting sqref="C8:E10">
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="D7:F9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0.3"/>
@@ -998,7 +1304,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C13:E13">
+  <conditionalFormatting sqref="D12:F12">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0.3"/>
@@ -1011,7 +1317,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="decimal" sqref="H6" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="decimal" sqref="I6" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0.4</formula1>
       <formula2>0.6</formula2>
     </dataValidation>
@@ -1024,13 +1330,13 @@
           <x14:formula1>
             <xm:f>Parameters!$B$7:$B$10</xm:f>
           </x14:formula1>
-          <xm:sqref>H7:H8</xm:sqref>
+          <xm:sqref>I7:I8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
             <xm:f>Parameters!$G$7:$G$9</xm:f>
           </x14:formula1>
-          <xm:sqref>H9:H10</xm:sqref>
+          <xm:sqref>I9:I10</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1055,7 +1361,7 @@
     <col min="10" max="11" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1068,33 +1374,23 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
+      <c r="B2" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
@@ -1111,132 +1407,132 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
+      <c r="B5" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
+      <c r="G5" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
+      <c r="B6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>28</v>
+      <c r="G6" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="11">
+      <c r="B7" s="16">
         <v>300</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="17">
         <v>2918</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="17">
         <v>2918</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="13">
+      <c r="G7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="18">
         <v>1.02</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="18">
         <v>1.02</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="11">
+      <c r="B8" s="19">
         <v>320</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="17">
         <v>3113</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="17">
         <v>3113</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="13">
+      <c r="G8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="18">
         <v>0.96499999999999997</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="18">
         <v>0.96499999999999997</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="11">
+      <c r="B9" s="16">
         <v>355</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="17">
         <v>3454</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="17">
         <v>3454</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="13">
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="18">
         <v>0.875</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="18">
         <v>0.875</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="11">
+      <c r="B10" s="19">
         <v>370</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="17">
         <v>3600</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="17">
         <v>3600</v>
       </c>
       <c r="E10" s="1"/>
@@ -1267,82 +1563,62 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
+      <c r="B13" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>28</v>
+      <c r="B14" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="12">
+      <c r="B15" s="20">
         <v>17.420000000000002</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="18">
         <v>1.19</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="18">
         <v>1.19</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="12">
+      <c r="B16" s="21">
         <v>19</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="18">
         <v>1</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="18">
         <v>1</v>
       </c>
       <c r="E16" s="1"/>
@@ -1353,15 +1629,15 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="12">
+      <c r="B17" s="20">
         <v>21.38</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="18">
         <v>0.79</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="18">
         <v>0.79</v>
       </c>
       <c r="E17" s="1"/>
@@ -1385,108 +1661,38 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
     <row r="21" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
     <row r="22" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
     <row r="23" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
     </row>
@@ -1504,25 +1710,13 @@
       <c r="K26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="4">
     <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B21:I21"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="decimal" operator="greaterThan" sqref="C7:D10 H7:I9 C15:D17" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
@@ -1547,7 +1741,7 @@
     <col min="9" max="10" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1559,31 +1753,22 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="B2" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
@@ -1599,16 +1784,16 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>48</v>
+      <c r="B5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1617,17 +1802,17 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="14">
-        <f>INDEX(Parameters!$C$7:$C$10,MATCH('Balance Map'!$H$7,Parameters!$B$7:$B$10,0))</f>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="22">
+        <f>INDEX(Parameters!$C$7:$C$10,MATCH('Balance Map'!$I$7,Parameters!$B$7:$B$10,0))</f>
         <v>3454</v>
       </c>
-      <c r="D6" s="14">
-        <f>INDEX(Parameters!$D$7:$D$10,MATCH('Balance Map'!$H$8,Parameters!$B$7:$B$10,0))</f>
+      <c r="D6" s="22">
+        <f>INDEX(Parameters!$D$7:$D$10,MATCH('Balance Map'!$I$8,Parameters!$B$7:$B$10,0))</f>
         <v>3454</v>
       </c>
       <c r="E6" s="1"/>
@@ -1637,17 +1822,17 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="14">
-        <f>INDEX(Parameters!$H$7:$H$9,MATCH('Balance Map'!$H$9,Parameters!$G$7:$G$9,0))</f>
+      <c r="B7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="23">
+        <f>INDEX(Parameters!$H$7:$H$9,MATCH('Balance Map'!$I$9,Parameters!$G$7:$G$9,0))</f>
         <v>1.02</v>
       </c>
-      <c r="D7" s="14">
-        <f>INDEX(Parameters!$I$7:$I$9,MATCH('Balance Map'!$H$10,Parameters!$G$7:$G$9,0))</f>
+      <c r="D7" s="23">
+        <f>INDEX(Parameters!$I$7:$I$9,MATCH('Balance Map'!$I$10,Parameters!$G$7:$G$9,0))</f>
         <v>1.02</v>
       </c>
       <c r="E7" s="1"/>
@@ -1657,17 +1842,17 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="14">
-        <f>C6*C7*'Balance Map'!$H$6</f>
+      <c r="B8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="22">
+        <f>C6*C7*'Balance Map'!$I$6</f>
         <v>1832.0016000000001</v>
       </c>
-      <c r="D8" s="14">
-        <f>D6*D7*(1-'Balance Map'!$H$6)</f>
+      <c r="D8" s="22">
+        <f>D6*D7*(1-'Balance Map'!$I$6)</f>
         <v>1691.0783999999999</v>
       </c>
       <c r="E8" s="1"/>
@@ -1701,337 +1886,337 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
+      <c r="B11" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>59</v>
+      <c r="B12" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>41</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="12">
+      <c r="B13" s="20">
         <f>Parameters!B15</f>
         <v>17.420000000000002</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="20">
         <f>Parameters!B15</f>
         <v>17.420000000000002</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="22">
         <f>Parameters!C15</f>
         <v>1.19</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="22">
         <f>Parameters!D15</f>
         <v>1.19</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="22">
         <f t="shared" ref="F13:F21" si="0">$C$8*D13</f>
         <v>2180.0819040000001</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="22">
         <f t="shared" ref="G13:G21" si="1">$D$8*E13</f>
         <v>2012.3832959999997</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="24">
         <f t="shared" ref="H13:H21" si="2">F13/(F13+G13)</f>
         <v>0.52000000000000013</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="12">
+      <c r="B14" s="21">
         <f>Parameters!B15</f>
         <v>17.420000000000002</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="21">
         <f>Parameters!B16</f>
         <v>19</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="23">
         <f>Parameters!C15</f>
         <v>1.19</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="23">
         <f>Parameters!D16</f>
         <v>1</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="23">
         <f t="shared" si="0"/>
         <v>2180.0819040000001</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="23">
         <f t="shared" si="1"/>
         <v>1691.0783999999999</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="25">
         <f t="shared" si="2"/>
         <v>0.5631598107025847</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="12">
+      <c r="B15" s="20">
         <f>Parameters!B15</f>
         <v>17.420000000000002</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="20">
         <f>Parameters!B17</f>
         <v>21.38</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="22">
         <f>Parameters!C15</f>
         <v>1.19</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="22">
         <f>Parameters!D17</f>
         <v>0.79</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="22">
         <f t="shared" si="0"/>
         <v>2180.0819040000001</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="22">
         <f t="shared" si="1"/>
         <v>1335.9519359999999</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="24">
         <f t="shared" si="2"/>
         <v>0.62004008016032064</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="12">
+      <c r="B16" s="21">
         <f>Parameters!B16</f>
         <v>19</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="21">
         <f>Parameters!B15</f>
         <v>17.420000000000002</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="23">
         <f>Parameters!C16</f>
         <v>1</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="23">
         <f>Parameters!D15</f>
         <v>1.19</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="23">
         <f t="shared" si="0"/>
         <v>1832.0016000000001</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="23">
         <f t="shared" si="1"/>
         <v>2012.3832959999997</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="25">
         <f t="shared" si="2"/>
         <v>0.47653958944281533</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="12">
+      <c r="B17" s="20">
         <f>Parameters!B16</f>
         <v>19</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="20">
         <f>Parameters!B16</f>
         <v>19</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="22">
         <f>Parameters!C16</f>
         <v>1</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="22">
         <f>Parameters!D16</f>
         <v>1</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="22">
         <f t="shared" si="0"/>
         <v>1832.0016000000001</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="22">
         <f t="shared" si="1"/>
         <v>1691.0783999999999</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="24">
         <f t="shared" si="2"/>
         <v>0.52</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="12">
+      <c r="B18" s="21">
         <f>Parameters!B16</f>
         <v>19</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="21">
         <f>Parameters!B17</f>
         <v>21.38</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="23">
         <f>Parameters!C16</f>
         <v>1</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="23">
         <f>Parameters!D17</f>
         <v>0.79</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="23">
         <f t="shared" si="0"/>
         <v>1832.0016000000001</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="23">
         <f t="shared" si="1"/>
         <v>1335.9519359999999</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="25">
         <f t="shared" si="2"/>
         <v>0.57829181494661919</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="12">
+      <c r="B19" s="20">
         <f>Parameters!B17</f>
         <v>21.38</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="20">
         <f>Parameters!B15</f>
         <v>17.420000000000002</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="22">
         <f>Parameters!C17</f>
         <v>0.79</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="22">
         <f>Parameters!D15</f>
         <v>1.19</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="22">
         <f t="shared" si="0"/>
         <v>1447.2812640000002</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="22">
         <f t="shared" si="1"/>
         <v>2012.3832959999997</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="24">
         <f t="shared" si="2"/>
         <v>0.4183299389002037</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="12">
+      <c r="B20" s="21">
         <f>Parameters!B17</f>
         <v>21.38</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="21">
         <f>Parameters!B16</f>
         <v>19</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="23">
         <f>Parameters!C17</f>
         <v>0.79</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="23">
         <f>Parameters!D16</f>
         <v>1</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="23">
         <f t="shared" si="0"/>
         <v>1447.2812640000002</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="23">
         <f t="shared" si="1"/>
         <v>1691.0783999999999</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="25">
         <f t="shared" si="2"/>
         <v>0.46115850920520884</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="12">
+      <c r="B21" s="20">
         <f>Parameters!B17</f>
         <v>21.38</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="20">
         <f>Parameters!B17</f>
         <v>21.38</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="22">
         <f>Parameters!C17</f>
         <v>0.79</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="22">
         <f>Parameters!D17</f>
         <v>0.79</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="22">
         <f t="shared" si="0"/>
         <v>1447.2812640000002</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="22">
         <f t="shared" si="1"/>
         <v>1335.9519359999999</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="24">
         <f t="shared" si="2"/>
         <v>0.52</v>
       </c>
@@ -2087,12 +2272,12 @@
       <c r="J25" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
     <mergeCell ref="B11:H11"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/brake_balance.xlsx
+++ b/docs/brake_balance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3B56B9-BA01-482A-B0FA-8B83562A53B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6E8107-D6B2-4C7B-9BF0-A47AAF8A3AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -753,23 +753,23 @@
     <xf numFmtId="10" fontId="28" fillId="27" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1045,23 +1045,23 @@
     </row>
     <row r="5" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="30" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="I5" s="28"/>
+      <c r="I5" s="29"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="28" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="8">
@@ -1081,28 +1081,28 @@
         <v>3</v>
       </c>
       <c r="I6" s="4">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="29"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="8">
         <f>Parameters!B15</f>
         <v>17.420000000000002</v>
       </c>
       <c r="D7" s="9">
         <f>Calculations!H13</f>
-        <v>0.52000000000000013</v>
+        <v>0.54</v>
       </c>
       <c r="E7" s="9">
         <f>Calculations!H14</f>
-        <v>0.5631598107025847</v>
+        <v>0.582804280790858</v>
       </c>
       <c r="F7" s="9">
         <f>Calculations!H15</f>
-        <v>0.62004008016032064</v>
+        <v>0.63876739562624263</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="6" t="s">
@@ -1115,22 +1115,22 @@
     </row>
     <row r="8" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="29"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="10">
         <f>Parameters!B16</f>
         <v>19</v>
       </c>
       <c r="D8" s="9">
         <f>Calculations!H16</f>
-        <v>0.47653958944281533</v>
+        <v>0.49659738826558769</v>
       </c>
       <c r="E8" s="9">
         <f>Calculations!H17</f>
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="F8" s="9">
         <f>Calculations!H18</f>
-        <v>0.57829181494661919</v>
+        <v>0.59774186406907248</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="3" t="s">
@@ -1143,22 +1143,22 @@
     </row>
     <row r="9" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="29"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="8">
         <f>Parameters!B17</f>
         <v>21.38</v>
       </c>
       <c r="D9" s="9">
         <f>Calculations!H19</f>
-        <v>0.4183299389002037</v>
+        <v>0.43798767967145796</v>
       </c>
       <c r="E9" s="9">
         <f>Calculations!H20</f>
-        <v>0.46115850920520884</v>
+        <v>0.48116399729302961</v>
       </c>
       <c r="F9" s="9">
         <f>Calculations!H21</f>
-        <v>0.52</v>
+        <v>0.54000000000000015</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="6" t="s">
@@ -1376,16 +1376,16 @@
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
@@ -1409,18 +1409,18 @@
     </row>
     <row r="5" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
@@ -1568,11 +1568,11 @@
     </row>
     <row r="13" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="J13" s="1"/>
@@ -1755,15 +1755,15 @@
     </row>
     <row r="2" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
@@ -1849,11 +1849,11 @@
       </c>
       <c r="C8" s="22">
         <f>C6*C7*'Balance Map'!$I$6</f>
-        <v>1832.0016000000001</v>
+        <v>1902.4632000000001</v>
       </c>
       <c r="D8" s="22">
         <f>D6*D7*(1-'Balance Map'!$I$6)</f>
-        <v>1691.0783999999999</v>
+        <v>1620.6167999999998</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -1888,15 +1888,15 @@
     </row>
     <row r="11" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
@@ -1946,15 +1946,15 @@
       </c>
       <c r="F13" s="22">
         <f t="shared" ref="F13:F21" si="0">$C$8*D13</f>
-        <v>2180.0819040000001</v>
+        <v>2263.931208</v>
       </c>
       <c r="G13" s="22">
         <f t="shared" ref="G13:G21" si="1">$D$8*E13</f>
-        <v>2012.3832959999997</v>
+        <v>1928.5339919999997</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" ref="H13:H21" si="2">F13/(F13+G13)</f>
-        <v>0.52000000000000013</v>
+        <v>0.54</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1979,15 +1979,15 @@
       </c>
       <c r="F14" s="23">
         <f t="shared" si="0"/>
-        <v>2180.0819040000001</v>
+        <v>2263.931208</v>
       </c>
       <c r="G14" s="23">
         <f t="shared" si="1"/>
-        <v>1691.0783999999999</v>
+        <v>1620.6167999999998</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="2"/>
-        <v>0.5631598107025847</v>
+        <v>0.582804280790858</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -2012,15 +2012,15 @@
       </c>
       <c r="F15" s="22">
         <f t="shared" si="0"/>
-        <v>2180.0819040000001</v>
+        <v>2263.931208</v>
       </c>
       <c r="G15" s="22">
         <f t="shared" si="1"/>
-        <v>1335.9519359999999</v>
+        <v>1280.2872719999998</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="2"/>
-        <v>0.62004008016032064</v>
+        <v>0.63876739562624263</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -2045,15 +2045,15 @@
       </c>
       <c r="F16" s="23">
         <f t="shared" si="0"/>
-        <v>1832.0016000000001</v>
+        <v>1902.4632000000001</v>
       </c>
       <c r="G16" s="23">
         <f t="shared" si="1"/>
-        <v>2012.3832959999997</v>
+        <v>1928.5339919999997</v>
       </c>
       <c r="H16" s="25">
         <f t="shared" si="2"/>
-        <v>0.47653958944281533</v>
+        <v>0.49659738826558769</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -2078,15 +2078,15 @@
       </c>
       <c r="F17" s="22">
         <f t="shared" si="0"/>
-        <v>1832.0016000000001</v>
+        <v>1902.4632000000001</v>
       </c>
       <c r="G17" s="22">
         <f t="shared" si="1"/>
-        <v>1691.0783999999999</v>
+        <v>1620.6167999999998</v>
       </c>
       <c r="H17" s="24">
         <f t="shared" si="2"/>
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -2111,15 +2111,15 @@
       </c>
       <c r="F18" s="23">
         <f t="shared" si="0"/>
-        <v>1832.0016000000001</v>
+        <v>1902.4632000000001</v>
       </c>
       <c r="G18" s="23">
         <f t="shared" si="1"/>
-        <v>1335.9519359999999</v>
+        <v>1280.2872719999998</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="2"/>
-        <v>0.57829181494661919</v>
+        <v>0.59774186406907248</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -2144,15 +2144,15 @@
       </c>
       <c r="F19" s="22">
         <f t="shared" si="0"/>
-        <v>1447.2812640000002</v>
+        <v>1502.9459280000001</v>
       </c>
       <c r="G19" s="22">
         <f t="shared" si="1"/>
-        <v>2012.3832959999997</v>
+        <v>1928.5339919999997</v>
       </c>
       <c r="H19" s="24">
         <f t="shared" si="2"/>
-        <v>0.4183299389002037</v>
+        <v>0.43798767967145796</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -2177,15 +2177,15 @@
       </c>
       <c r="F20" s="23">
         <f t="shared" si="0"/>
-        <v>1447.2812640000002</v>
+        <v>1502.9459280000001</v>
       </c>
       <c r="G20" s="23">
         <f t="shared" si="1"/>
-        <v>1691.0783999999999</v>
+        <v>1620.6167999999998</v>
       </c>
       <c r="H20" s="25">
         <f t="shared" si="2"/>
-        <v>0.46115850920520884</v>
+        <v>0.48116399729302961</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -2210,15 +2210,15 @@
       </c>
       <c r="F21" s="22">
         <f t="shared" si="0"/>
-        <v>1447.2812640000002</v>
+        <v>1502.9459280000001</v>
       </c>
       <c r="G21" s="22">
         <f t="shared" si="1"/>
-        <v>1335.9519359999999</v>
+        <v>1280.2872719999998</v>
       </c>
       <c r="H21" s="24">
         <f t="shared" si="2"/>
-        <v>0.52</v>
+        <v>0.54000000000000015</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>

--- a/docs/brake_balance.xlsx
+++ b/docs/brake_balance.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\brake-final-178-20261026\outputs\brake-final-178-20261026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6E8107-D6B2-4C7B-9BF0-A47AAF8A3AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1B3D13-3C09-49B7-90D1-256EF2B8EB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>Astral · Brake balance</t>
   </si>
@@ -161,6 +161,10 @@
   </si>
   <si>
     <t>Front share</t>
+  </si>
+  <si>
+    <t>Type-A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -674,7 +678,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -755,6 +759,18 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="20" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="24" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="25" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="25" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1046,63 +1062,63 @@
     <row r="5" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="26"/>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="I5" s="29"/>
+      <c r="I5" s="33"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="32" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="8">
         <f>Parameters!B15</f>
-        <v>17.420000000000002</v>
+        <v>17.8</v>
       </c>
       <c r="E6" s="10">
         <f>Parameters!B16</f>
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="F6" s="8">
         <f>Parameters!B17</f>
-        <v>21.38</v>
+        <v>21.5</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I6" s="4">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="28"/>
+      <c r="B7" s="32"/>
       <c r="C7" s="8">
         <f>Parameters!B15</f>
-        <v>17.420000000000002</v>
+        <v>17.8</v>
       </c>
       <c r="D7" s="9">
         <f>Calculations!H13</f>
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="E7" s="9">
         <f>Calculations!H14</f>
-        <v>0.582804280790858</v>
+        <v>0.63799831008914742</v>
       </c>
       <c r="F7" s="9">
         <f>Calculations!H15</f>
-        <v>0.63876739562624263</v>
+        <v>0.67727923242829213</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="6" t="s">
@@ -1115,22 +1131,22 @@
     </row>
     <row r="8" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="28"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="10">
         <f>Parameters!B16</f>
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="D8" s="9">
         <f>Calculations!H16</f>
-        <v>0.49659738826558769</v>
+        <v>0.54022388720968006</v>
       </c>
       <c r="E8" s="9">
         <f>Calculations!H17</f>
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="F8" s="9">
         <f>Calculations!H18</f>
-        <v>0.59774186406907248</v>
+        <v>0.63148082079847156</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="3" t="s">
@@ -1143,29 +1159,29 @@
     </row>
     <row r="9" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="28"/>
+      <c r="B9" s="32"/>
       <c r="C9" s="8">
         <f>Parameters!B17</f>
-        <v>21.38</v>
+        <v>21.5</v>
       </c>
       <c r="D9" s="9">
         <f>Calculations!H19</f>
-        <v>0.43798767967145796</v>
+        <v>0.49665869063786672</v>
       </c>
       <c r="E9" s="9">
         <f>Calculations!H20</f>
-        <v>0.48116399729302961</v>
+        <v>0.54719804296452867</v>
       </c>
       <c r="F9" s="9">
         <f>Calculations!H21</f>
-        <v>0.54000000000000015</v>
+        <v>0.59</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="6" t="s">
         <v>7</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="J9" s="1"/>
     </row>
@@ -1181,7 +1197,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="J10" s="1"/>
     </row>
@@ -1376,16 +1392,16 @@
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
@@ -1409,18 +1425,18 @@
     </row>
     <row r="5" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
@@ -1455,21 +1471,21 @@
         <v>300</v>
       </c>
       <c r="C7" s="17">
-        <v>2918</v>
+        <v>3509</v>
       </c>
       <c r="D7" s="17">
-        <v>2918</v>
+        <v>3509</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="18">
-        <v>1.02</v>
-      </c>
-      <c r="I7" s="18">
-        <v>1.02</v>
+      <c r="H7" s="27">
+        <v>0.72</v>
+      </c>
+      <c r="I7" s="27">
+        <v>0.72</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1480,21 +1496,21 @@
         <v>320</v>
       </c>
       <c r="C8" s="17">
-        <v>3113</v>
+        <v>3743</v>
       </c>
       <c r="D8" s="17">
-        <v>3113</v>
+        <v>3743</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="18">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="I8" s="18">
-        <v>0.96499999999999997</v>
+      <c r="H8" s="27">
+        <v>0.68</v>
+      </c>
+      <c r="I8" s="27">
+        <v>0.68</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1505,21 +1521,21 @@
         <v>355</v>
       </c>
       <c r="C9" s="17">
-        <v>3454</v>
+        <v>4153</v>
       </c>
       <c r="D9" s="17">
-        <v>3454</v>
+        <v>4153</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="18">
-        <v>0.875</v>
-      </c>
-      <c r="I9" s="18">
-        <v>0.875</v>
+      <c r="H9" s="27">
+        <v>0.65</v>
+      </c>
+      <c r="I9" s="27">
+        <v>0.65</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1530,10 +1546,10 @@
         <v>370</v>
       </c>
       <c r="C10" s="17">
-        <v>3600</v>
+        <v>4329</v>
       </c>
       <c r="D10" s="17">
-        <v>3600</v>
+        <v>4329</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -1568,11 +1584,11 @@
     </row>
     <row r="13" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="J13" s="1"/>
@@ -1597,13 +1613,13 @@
     <row r="15" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="20">
-        <v>17.420000000000002</v>
+        <v>17.8</v>
       </c>
       <c r="C15" s="18">
-        <v>1.19</v>
+        <v>1.139</v>
       </c>
       <c r="D15" s="18">
-        <v>1.19</v>
+        <v>1.139</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -1613,13 +1629,13 @@
     <row r="16" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="21">
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="C16" s="18">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="D16" s="18">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -1632,13 +1648,13 @@
     <row r="17" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="20">
-        <v>21.38</v>
+        <v>21.5</v>
       </c>
       <c r="C17" s="18">
-        <v>0.79</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="D17" s="18">
-        <v>0.79</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1755,15 +1771,15 @@
     </row>
     <row r="2" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
@@ -1807,13 +1823,13 @@
       <c r="B6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="28">
         <f>INDEX(Parameters!$C$7:$C$10,MATCH('Balance Map'!$I$7,Parameters!$B$7:$B$10,0))</f>
-        <v>3454</v>
-      </c>
-      <c r="D6" s="22">
+        <v>4153</v>
+      </c>
+      <c r="D6" s="28">
         <f>INDEX(Parameters!$D$7:$D$10,MATCH('Balance Map'!$I$8,Parameters!$B$7:$B$10,0))</f>
-        <v>3454</v>
+        <v>4153</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -1827,13 +1843,13 @@
       <c r="B7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="29">
         <f>INDEX(Parameters!$H$7:$H$9,MATCH('Balance Map'!$I$9,Parameters!$G$7:$G$9,0))</f>
-        <v>1.02</v>
-      </c>
-      <c r="D7" s="23">
+        <v>0.72</v>
+      </c>
+      <c r="D7" s="29">
         <f>INDEX(Parameters!$I$7:$I$9,MATCH('Balance Map'!$I$10,Parameters!$G$7:$G$9,0))</f>
-        <v>1.02</v>
+        <v>0.72</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -1847,13 +1863,13 @@
       <c r="B8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="28">
         <f>C6*C7*'Balance Map'!$I$6</f>
-        <v>1902.4632000000001</v>
-      </c>
-      <c r="D8" s="22">
+        <v>1764.1943999999999</v>
+      </c>
+      <c r="D8" s="28">
         <f>D6*D7*(1-'Balance Map'!$I$6)</f>
-        <v>1620.6167999999998</v>
+        <v>1225.9656</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -1888,15 +1904,15 @@
     </row>
     <row r="11" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
@@ -1930,31 +1946,31 @@
       <c r="A13" s="1"/>
       <c r="B13" s="20">
         <f>Parameters!B15</f>
-        <v>17.420000000000002</v>
+        <v>17.8</v>
       </c>
       <c r="C13" s="20">
         <f>Parameters!B15</f>
-        <v>17.420000000000002</v>
+        <v>17.8</v>
       </c>
       <c r="D13" s="22">
         <f>Parameters!C15</f>
-        <v>1.19</v>
+        <v>1.139</v>
       </c>
       <c r="E13" s="22">
         <f>Parameters!D15</f>
-        <v>1.19</v>
-      </c>
-      <c r="F13" s="22">
+        <v>1.139</v>
+      </c>
+      <c r="F13" s="28">
         <f t="shared" ref="F13:F21" si="0">$C$8*D13</f>
-        <v>2263.931208</v>
-      </c>
-      <c r="G13" s="22">
+        <v>2009.4174215999999</v>
+      </c>
+      <c r="G13" s="28">
         <f t="shared" ref="G13:G21" si="1">$D$8*E13</f>
-        <v>1928.5339919999997</v>
+        <v>1396.3748184000001</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" ref="H13:H21" si="2">F13/(F13+G13)</f>
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1963,31 +1979,31 @@
       <c r="A14" s="1"/>
       <c r="B14" s="21">
         <f>Parameters!B15</f>
-        <v>17.420000000000002</v>
+        <v>17.8</v>
       </c>
       <c r="C14" s="21">
         <f>Parameters!B16</f>
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="D14" s="23">
         <f>Parameters!C15</f>
-        <v>1.19</v>
+        <v>1.139</v>
       </c>
       <c r="E14" s="23">
         <f>Parameters!D16</f>
-        <v>1</v>
-      </c>
-      <c r="F14" s="23">
+        <v>0.93</v>
+      </c>
+      <c r="F14" s="30">
         <f t="shared" si="0"/>
-        <v>2263.931208</v>
-      </c>
-      <c r="G14" s="23">
+        <v>2009.4174215999999</v>
+      </c>
+      <c r="G14" s="30">
         <f t="shared" si="1"/>
-        <v>1620.6167999999998</v>
+        <v>1140.1480080000001</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="2"/>
-        <v>0.582804280790858</v>
+        <v>0.63799831008914742</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1996,31 +2012,31 @@
       <c r="A15" s="1"/>
       <c r="B15" s="20">
         <f>Parameters!B15</f>
-        <v>17.420000000000002</v>
+        <v>17.8</v>
       </c>
       <c r="C15" s="20">
         <f>Parameters!B17</f>
-        <v>21.38</v>
+        <v>21.5</v>
       </c>
       <c r="D15" s="22">
         <f>Parameters!C15</f>
-        <v>1.19</v>
+        <v>1.139</v>
       </c>
       <c r="E15" s="22">
         <f>Parameters!D17</f>
-        <v>0.79</v>
-      </c>
-      <c r="F15" s="22">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="F15" s="28">
         <f t="shared" si="0"/>
-        <v>2263.931208</v>
-      </c>
-      <c r="G15" s="22">
+        <v>2009.4174215999999</v>
+      </c>
+      <c r="G15" s="28">
         <f t="shared" si="1"/>
-        <v>1280.2872719999998</v>
+        <v>957.47913360000007</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="2"/>
-        <v>0.63876739562624263</v>
+        <v>0.67727923242829213</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -2029,31 +2045,31 @@
       <c r="A16" s="1"/>
       <c r="B16" s="21">
         <f>Parameters!B16</f>
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="C16" s="21">
         <f>Parameters!B15</f>
-        <v>17.420000000000002</v>
+        <v>17.8</v>
       </c>
       <c r="D16" s="23">
         <f>Parameters!C16</f>
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="E16" s="23">
         <f>Parameters!D15</f>
-        <v>1.19</v>
-      </c>
-      <c r="F16" s="23">
+        <v>1.139</v>
+      </c>
+      <c r="F16" s="30">
         <f t="shared" si="0"/>
-        <v>1902.4632000000001</v>
-      </c>
-      <c r="G16" s="23">
+        <v>1640.7007919999999</v>
+      </c>
+      <c r="G16" s="30">
         <f t="shared" si="1"/>
-        <v>1928.5339919999997</v>
+        <v>1396.3748184000001</v>
       </c>
       <c r="H16" s="25">
         <f t="shared" si="2"/>
-        <v>0.49659738826558769</v>
+        <v>0.54022388720968006</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -2062,31 +2078,31 @@
       <c r="A17" s="1"/>
       <c r="B17" s="20">
         <f>Parameters!B16</f>
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="C17" s="20">
         <f>Parameters!B16</f>
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="D17" s="22">
         <f>Parameters!C16</f>
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="E17" s="22">
         <f>Parameters!D16</f>
-        <v>1</v>
-      </c>
-      <c r="F17" s="22">
+        <v>0.93</v>
+      </c>
+      <c r="F17" s="28">
         <f t="shared" si="0"/>
-        <v>1902.4632000000001</v>
-      </c>
-      <c r="G17" s="22">
+        <v>1640.7007919999999</v>
+      </c>
+      <c r="G17" s="28">
         <f t="shared" si="1"/>
-        <v>1620.6167999999998</v>
+        <v>1140.1480080000001</v>
       </c>
       <c r="H17" s="24">
         <f t="shared" si="2"/>
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -2095,31 +2111,31 @@
       <c r="A18" s="1"/>
       <c r="B18" s="21">
         <f>Parameters!B16</f>
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="C18" s="21">
         <f>Parameters!B17</f>
-        <v>21.38</v>
+        <v>21.5</v>
       </c>
       <c r="D18" s="23">
         <f>Parameters!C16</f>
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="E18" s="23">
         <f>Parameters!D17</f>
-        <v>0.79</v>
-      </c>
-      <c r="F18" s="23">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="F18" s="30">
         <f t="shared" si="0"/>
-        <v>1902.4632000000001</v>
-      </c>
-      <c r="G18" s="23">
+        <v>1640.7007919999999</v>
+      </c>
+      <c r="G18" s="30">
         <f t="shared" si="1"/>
-        <v>1280.2872719999998</v>
+        <v>957.47913360000007</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="2"/>
-        <v>0.59774186406907248</v>
+        <v>0.63148082079847156</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -2128,31 +2144,31 @@
       <c r="A19" s="1"/>
       <c r="B19" s="20">
         <f>Parameters!B17</f>
-        <v>21.38</v>
+        <v>21.5</v>
       </c>
       <c r="C19" s="20">
         <f>Parameters!B15</f>
-        <v>17.420000000000002</v>
+        <v>17.8</v>
       </c>
       <c r="D19" s="22">
         <f>Parameters!C17</f>
-        <v>0.79</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="E19" s="22">
         <f>Parameters!D15</f>
-        <v>1.19</v>
-      </c>
-      <c r="F19" s="22">
+        <v>1.139</v>
+      </c>
+      <c r="F19" s="28">
         <f t="shared" si="0"/>
-        <v>1502.9459280000001</v>
-      </c>
-      <c r="G19" s="22">
+        <v>1377.8358263999999</v>
+      </c>
+      <c r="G19" s="28">
         <f t="shared" si="1"/>
-        <v>1928.5339919999997</v>
+        <v>1396.3748184000001</v>
       </c>
       <c r="H19" s="24">
         <f t="shared" si="2"/>
-        <v>0.43798767967145796</v>
+        <v>0.49665869063786672</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -2161,31 +2177,31 @@
       <c r="A20" s="1"/>
       <c r="B20" s="21">
         <f>Parameters!B17</f>
-        <v>21.38</v>
+        <v>21.5</v>
       </c>
       <c r="C20" s="21">
         <f>Parameters!B16</f>
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="D20" s="23">
         <f>Parameters!C17</f>
-        <v>0.79</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="E20" s="23">
         <f>Parameters!D16</f>
-        <v>1</v>
-      </c>
-      <c r="F20" s="23">
+        <v>0.93</v>
+      </c>
+      <c r="F20" s="30">
         <f t="shared" si="0"/>
-        <v>1502.9459280000001</v>
-      </c>
-      <c r="G20" s="23">
+        <v>1377.8358263999999</v>
+      </c>
+      <c r="G20" s="30">
         <f t="shared" si="1"/>
-        <v>1620.6167999999998</v>
+        <v>1140.1480080000001</v>
       </c>
       <c r="H20" s="25">
         <f t="shared" si="2"/>
-        <v>0.48116399729302961</v>
+        <v>0.54719804296452867</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -2194,31 +2210,31 @@
       <c r="A21" s="1"/>
       <c r="B21" s="20">
         <f>Parameters!B17</f>
-        <v>21.38</v>
+        <v>21.5</v>
       </c>
       <c r="C21" s="20">
         <f>Parameters!B17</f>
-        <v>21.38</v>
+        <v>21.5</v>
       </c>
       <c r="D21" s="22">
         <f>Parameters!C17</f>
-        <v>0.79</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="E21" s="22">
         <f>Parameters!D17</f>
-        <v>0.79</v>
-      </c>
-      <c r="F21" s="22">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="F21" s="28">
         <f t="shared" si="0"/>
-        <v>1502.9459280000001</v>
-      </c>
-      <c r="G21" s="22">
+        <v>1377.8358263999999</v>
+      </c>
+      <c r="G21" s="28">
         <f t="shared" si="1"/>
-        <v>1280.2872719999998</v>
+        <v>957.47913360000007</v>
       </c>
       <c r="H21" s="24">
         <f t="shared" si="2"/>
-        <v>0.54000000000000015</v>
+        <v>0.59</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>

--- a/docs/brake_balance.xlsx
+++ b/docs/brake_balance.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\brake-final-178-20261026\outputs\brake-final-178-20261026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1B3D13-3C09-49B7-90D1-256EF2B8EB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F38E0D-29DD-4EFA-A7C6-EAFCC2E14572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>Astral · Brake balance</t>
   </si>
@@ -161,10 +161,6 @@
   </si>
   <si>
     <t>Front share</t>
-  </si>
-  <si>
-    <t>Type-A</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1097,7 +1093,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="4">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="J6" s="1"/>
     </row>
@@ -1110,22 +1106,22 @@
       </c>
       <c r="D7" s="9">
         <f>Calculations!H13</f>
-        <v>0.59</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="E7" s="9">
         <f>Calculations!H14</f>
-        <v>0.63799831008914742</v>
+        <v>0.64752700397953378</v>
       </c>
       <c r="F7" s="9">
         <f>Calculations!H15</f>
-        <v>0.67727923242829213</v>
+        <v>0.68628238602128944</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="6" t="s">
         <v>5</v>
       </c>
       <c r="I7" s="7">
-        <v>355</v>
+        <v>300</v>
       </c>
       <c r="J7" s="1"/>
     </row>
@@ -1138,22 +1134,22 @@
       </c>
       <c r="D8" s="9">
         <f>Calculations!H16</f>
-        <v>0.54022388720968006</v>
+        <v>0.55051302288871351</v>
       </c>
       <c r="E8" s="9">
         <f>Calculations!H17</f>
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="F8" s="9">
         <f>Calculations!H18</f>
-        <v>0.63148082079847156</v>
+        <v>0.64108455882352944</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I8" s="7">
-        <v>355</v>
+        <v>300</v>
       </c>
       <c r="J8" s="1"/>
     </row>
@@ -1166,22 +1162,22 @@
       </c>
       <c r="D9" s="9">
         <f>Calculations!H19</f>
-        <v>0.49665869063786672</v>
+        <v>0.50703310971651161</v>
       </c>
       <c r="E9" s="9">
         <f>Calculations!H20</f>
-        <v>0.54719804296452867</v>
+        <v>0.55745895788722333</v>
       </c>
       <c r="F9" s="9">
         <f>Calculations!H21</f>
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="6" t="s">
         <v>7</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="J9" s="1"/>
     </row>
@@ -1197,7 +1193,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="J10" s="1"/>
     </row>
@@ -1825,11 +1821,11 @@
       </c>
       <c r="C6" s="28">
         <f>INDEX(Parameters!$C$7:$C$10,MATCH('Balance Map'!$I$7,Parameters!$B$7:$B$10,0))</f>
-        <v>4153</v>
+        <v>3509</v>
       </c>
       <c r="D6" s="28">
         <f>INDEX(Parameters!$D$7:$D$10,MATCH('Balance Map'!$I$8,Parameters!$B$7:$B$10,0))</f>
-        <v>4153</v>
+        <v>3509</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -1845,11 +1841,11 @@
       </c>
       <c r="C7" s="29">
         <f>INDEX(Parameters!$H$7:$H$9,MATCH('Balance Map'!$I$9,Parameters!$G$7:$G$9,0))</f>
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="D7" s="29">
         <f>INDEX(Parameters!$I$7:$I$9,MATCH('Balance Map'!$I$10,Parameters!$G$7:$G$9,0))</f>
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -1865,11 +1861,11 @@
       </c>
       <c r="C8" s="28">
         <f>C6*C7*'Balance Map'!$I$6</f>
-        <v>1764.1943999999999</v>
+        <v>1368.51</v>
       </c>
       <c r="D8" s="28">
         <f>D6*D7*(1-'Balance Map'!$I$6)</f>
-        <v>1225.9656</v>
+        <v>912.34</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -1962,15 +1958,15 @@
       </c>
       <c r="F13" s="28">
         <f t="shared" ref="F13:F21" si="0">$C$8*D13</f>
-        <v>2009.4174215999999</v>
+        <v>1558.73289</v>
       </c>
       <c r="G13" s="28">
         <f t="shared" ref="G13:G21" si="1">$D$8*E13</f>
-        <v>1396.3748184000001</v>
+        <v>1039.15526</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" ref="H13:H21" si="2">F13/(F13+G13)</f>
-        <v>0.59</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1995,15 +1991,15 @@
       </c>
       <c r="F14" s="30">
         <f t="shared" si="0"/>
-        <v>2009.4174215999999</v>
+        <v>1558.73289</v>
       </c>
       <c r="G14" s="30">
         <f t="shared" si="1"/>
-        <v>1140.1480080000001</v>
+        <v>848.47620000000006</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="2"/>
-        <v>0.63799831008914742</v>
+        <v>0.64752700397953378</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -2028,15 +2024,15 @@
       </c>
       <c r="F15" s="28">
         <f t="shared" si="0"/>
-        <v>2009.4174215999999</v>
+        <v>1558.73289</v>
       </c>
       <c r="G15" s="28">
         <f t="shared" si="1"/>
-        <v>957.47913360000007</v>
+        <v>712.53754000000004</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="2"/>
-        <v>0.67727923242829213</v>
+        <v>0.68628238602128944</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -2061,15 +2057,15 @@
       </c>
       <c r="F16" s="30">
         <f t="shared" si="0"/>
-        <v>1640.7007919999999</v>
+        <v>1272.7143000000001</v>
       </c>
       <c r="G16" s="30">
         <f t="shared" si="1"/>
-        <v>1396.3748184000001</v>
+        <v>1039.15526</v>
       </c>
       <c r="H16" s="25">
         <f t="shared" si="2"/>
-        <v>0.54022388720968006</v>
+        <v>0.55051302288871351</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -2094,15 +2090,15 @@
       </c>
       <c r="F17" s="28">
         <f t="shared" si="0"/>
-        <v>1640.7007919999999</v>
+        <v>1272.7143000000001</v>
       </c>
       <c r="G17" s="28">
         <f t="shared" si="1"/>
-        <v>1140.1480080000001</v>
+        <v>848.47620000000006</v>
       </c>
       <c r="H17" s="24">
         <f t="shared" si="2"/>
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -2127,15 +2123,15 @@
       </c>
       <c r="F18" s="30">
         <f t="shared" si="0"/>
-        <v>1640.7007919999999</v>
+        <v>1272.7143000000001</v>
       </c>
       <c r="G18" s="30">
         <f t="shared" si="1"/>
-        <v>957.47913360000007</v>
+        <v>712.53754000000004</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="2"/>
-        <v>0.63148082079847156</v>
+        <v>0.64108455882352944</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -2160,15 +2156,15 @@
       </c>
       <c r="F19" s="28">
         <f t="shared" si="0"/>
-        <v>1377.8358263999999</v>
+        <v>1068.8063099999999</v>
       </c>
       <c r="G19" s="28">
         <f t="shared" si="1"/>
-        <v>1396.3748184000001</v>
+        <v>1039.15526</v>
       </c>
       <c r="H19" s="24">
         <f t="shared" si="2"/>
-        <v>0.49665869063786672</v>
+        <v>0.50703310971651161</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -2193,15 +2189,15 @@
       </c>
       <c r="F20" s="30">
         <f t="shared" si="0"/>
-        <v>1377.8358263999999</v>
+        <v>1068.8063099999999</v>
       </c>
       <c r="G20" s="30">
         <f t="shared" si="1"/>
-        <v>1140.1480080000001</v>
+        <v>848.47620000000006</v>
       </c>
       <c r="H20" s="25">
         <f t="shared" si="2"/>
-        <v>0.54719804296452867</v>
+        <v>0.55745895788722333</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -2226,15 +2222,15 @@
       </c>
       <c r="F21" s="28">
         <f t="shared" si="0"/>
-        <v>1377.8358263999999</v>
+        <v>1068.8063099999999</v>
       </c>
       <c r="G21" s="28">
         <f t="shared" si="1"/>
-        <v>957.47913360000007</v>
+        <v>712.53754000000004</v>
       </c>
       <c r="H21" s="24">
         <f t="shared" si="2"/>
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>

--- a/docs/brake_balance.xlsx
+++ b/docs/brake_balance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F38E0D-29DD-4EFA-A7C6-EAFCC2E14572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF95BFD3-9C65-43E6-BE3C-A10A9BAA71E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Balance Map" sheetId="1" r:id="rId1"/>
@@ -173,7 +173,7 @@
     <numFmt numFmtId="178" formatCode="0&quot; mm&quot;"/>
     <numFmt numFmtId="179" formatCode="0.000"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,11 +183,7 @@
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -200,59 +196,70 @@
       <sz val="20"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF667B91"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF195DB1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF667B91"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF195DB1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="22"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF195DB1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -265,6 +272,7 @@
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -278,56 +286,67 @@
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF195DB1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF195DB1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="28">
@@ -666,11 +685,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -678,115 +694,114 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="9" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="12" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="12" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="15" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="18" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="1" fontId="18" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="19" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="21" fillId="20" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="20" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="22" fillId="21" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="1" fontId="21" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="23" fillId="22" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="2" fontId="22" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="24" fillId="23" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="2" fontId="23" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="25" fillId="24" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="179" fontId="24" fillId="24" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="26" fillId="25" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="179" fontId="25" fillId="25" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="27" fillId="26" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="10" fontId="26" fillId="26" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="28" fillId="27" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="10" fontId="27" fillId="27" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="21" fillId="20" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="20" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="25" fillId="24" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="1" fontId="24" fillId="24" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="26" fillId="25" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="2" fontId="25" fillId="25" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="26" fillId="25" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="1" fontId="25" fillId="25" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1000,302 +1015,302 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.08203125" customWidth="1"/>
-    <col min="3" max="6" width="17.58203125" customWidth="1"/>
+    <col min="2" max="2" width="12.125" customWidth="1"/>
+    <col min="3" max="6" width="17.625" customWidth="1"/>
     <col min="7" max="7" width="4" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="3" customWidth="1"/>
-    <col min="11" max="11" width="29.08203125" customWidth="1"/>
+    <col min="11" max="11" width="29.125" customWidth="1"/>
     <col min="12" max="12" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="31" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="2"/>
       <c r="H5" s="33" t="s">
         <v>1</v>
       </c>
       <c r="I5" s="33"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2"/>
       <c r="B6" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="11">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="3" t="s">
+      <c r="G6" s="2"/>
+      <c r="H6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="5">
         <v>0.6</v>
       </c>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="51.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2"/>
       <c r="B7" s="32"/>
-      <c r="C7" s="8">
+      <c r="C7" s="9">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="10">
         <f>Calculations!H13</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="10">
         <f>Calculations!H14</f>
         <v>0.64752700397953378</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="10">
         <f>Calculations!H15</f>
         <v>0.68628238602128944</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="6" t="s">
+      <c r="G7" s="2"/>
+      <c r="H7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="8">
         <v>300</v>
       </c>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="51.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
       <c r="B8" s="32"/>
-      <c r="C8" s="10">
+      <c r="C8" s="11">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="10">
         <f>Calculations!H16</f>
         <v>0.55051302288871351</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="10">
         <f>Calculations!H17</f>
         <v>0.6</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="10">
         <f>Calculations!H18</f>
         <v>0.64108455882352944</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="3" t="s">
+      <c r="G8" s="2"/>
+      <c r="H8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="8">
         <v>300</v>
       </c>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="51.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
       <c r="B9" s="32"/>
-      <c r="C9" s="8">
+      <c r="C9" s="9">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="10">
         <f>Calculations!H19</f>
         <v>0.50703310971651161</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="10">
         <f>Calculations!H20</f>
         <v>0.55745895788722333</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="10">
         <f>Calculations!H21</f>
         <v>0.6</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="6" t="s">
+      <c r="G9" s="2"/>
+      <c r="H9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="3" t="s">
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="12" t="s">
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="14">
         <v>0.3</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="14">
         <v>0.5</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <v>0.7</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="14" t="s">
+      <c r="G12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
+      <c r="G13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1303,7 +1318,7 @@
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="H5:I5"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D7:F9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -1362,7 +1377,7 @@
     <tabColor rgb="FFC49A32"/>
   </sheetPr>
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1373,21 +1388,21 @@
     <col min="10" max="11" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:11" ht="35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
+    <row r="1" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
       <c r="B2" s="34" t="s">
         <v>14</v>
       </c>
@@ -1398,328 +1413,328 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
       <c r="I2" s="35"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2"/>
       <c r="B5" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
       <c r="G5" s="33" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="15" t="s">
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2"/>
+      <c r="B6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="15" t="s">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="16">
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2"/>
+      <c r="B7" s="17">
         <v>300</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="18">
         <v>3509</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <v>3509</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="3" t="s">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="28">
         <v>0.72</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="28">
         <v>0.72</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="19">
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="20">
         <v>320</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <v>3743</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <v>3743</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="6" t="s">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="28">
         <v>0.68</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="28">
         <v>0.68</v>
       </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="16">
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+      <c r="B9" s="17">
         <v>355</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="18">
         <v>4153</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <v>4153</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="3" t="s">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="28">
         <v>0.65</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="28">
         <v>0.65</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="19">
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="20">
         <v>370</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="18">
         <v>4329</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="18">
         <v>4329</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
       <c r="B13" s="33" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="33"/>
       <c r="D13" s="33"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="15" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="20">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="21">
         <v>17.8</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="19">
         <v>1.139</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="19">
         <v>1.139</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="21">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="22">
         <v>19.7</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="19">
         <v>0.93</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="19">
         <v>0.93</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="20">
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="21">
         <v>21.5</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="19">
         <v>0.78100000000000003</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="19">
         <v>0.78100000000000003</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-    </row>
-    <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1728,7 +1743,7 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="G5:I5"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="decimal" operator="greaterThan" sqref="C7:D10 H7:I9 C15:D17" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
@@ -1744,7 +1759,7 @@
     <tabColor rgb="FF93A0AC"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -1753,20 +1768,20 @@
     <col min="9" max="10" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
+    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
       <c r="B2" s="34" t="s">
         <v>27</v>
       </c>
@@ -1776,130 +1791,130 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="5" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2"/>
+      <c r="B5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3" t="s">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2"/>
+      <c r="B6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="29">
         <f>INDEX(Parameters!$C$7:$C$10,MATCH('Balance Map'!$I$7,Parameters!$B$7:$B$10,0))</f>
         <v>3509</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="29">
         <f>INDEX(Parameters!$D$7:$D$10,MATCH('Balance Map'!$I$8,Parameters!$B$7:$B$10,0))</f>
         <v>3509</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="6" t="s">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2"/>
+      <c r="B7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <f>INDEX(Parameters!$H$7:$H$9,MATCH('Balance Map'!$I$9,Parameters!$G$7:$G$9,0))</f>
         <v>0.65</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>INDEX(Parameters!$I$7:$I$9,MATCH('Balance Map'!$I$10,Parameters!$G$7:$G$9,0))</f>
         <v>0.65</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="3" t="s">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <f>C6*C7*'Balance Map'!$I$6</f>
         <v>1368.51</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <f>D6*D7*(1-'Balance Map'!$I$6)</f>
         <v>912.34</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
       <c r="B11" s="33" t="s">
         <v>34</v>
       </c>
@@ -1909,386 +1924,386 @@
       <c r="F11" s="33"/>
       <c r="G11" s="33"/>
       <c r="H11" s="33"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="15" t="s">
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="20">
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="21">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="23">
         <f>Parameters!C15</f>
         <v>1.139</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="23">
         <f>Parameters!D15</f>
         <v>1.139</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="29">
         <f t="shared" ref="F13:F21" si="0">$C$8*D13</f>
         <v>1558.73289</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="29">
         <f t="shared" ref="G13:G21" si="1">$D$8*E13</f>
         <v>1039.15526</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="25">
         <f t="shared" ref="H13:H21" si="2">F13/(F13+G13)</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="21">
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="22">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="22">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="24">
         <f>Parameters!C15</f>
         <v>1.139</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="24">
         <f>Parameters!D16</f>
         <v>0.93</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f t="shared" si="0"/>
         <v>1558.73289</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <f t="shared" si="1"/>
         <v>848.47620000000006</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="26">
         <f t="shared" si="2"/>
         <v>0.64752700397953378</v>
       </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="20">
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="21">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="23">
         <f>Parameters!C15</f>
         <v>1.139</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="23">
         <f>Parameters!D17</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f t="shared" si="0"/>
         <v>1558.73289</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="29">
         <f t="shared" si="1"/>
         <v>712.53754000000004</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="25">
         <f t="shared" si="2"/>
         <v>0.68628238602128944</v>
       </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="21">
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="22">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="22">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="24">
         <f>Parameters!C16</f>
         <v>0.93</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="24">
         <f>Parameters!D15</f>
         <v>1.139</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <f t="shared" si="0"/>
         <v>1272.7143000000001</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <f t="shared" si="1"/>
         <v>1039.15526</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="26">
         <f t="shared" si="2"/>
         <v>0.55051302288871351</v>
       </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="20">
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="21">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="21">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="23">
         <f>Parameters!C16</f>
         <v>0.93</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="23">
         <f>Parameters!D16</f>
         <v>0.93</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="29">
         <f t="shared" si="0"/>
         <v>1272.7143000000001</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="29">
         <f t="shared" si="1"/>
         <v>848.47620000000006</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="25">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="21">
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="22">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="22">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="24">
         <f>Parameters!C16</f>
         <v>0.93</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="24">
         <f>Parameters!D17</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <f t="shared" si="0"/>
         <v>1272.7143000000001</v>
       </c>
-      <c r="G18" s="30">
+      <c r="G18" s="31">
         <f t="shared" si="1"/>
         <v>712.53754000000004</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="26">
         <f t="shared" si="2"/>
         <v>0.64108455882352944</v>
       </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="20">
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="21">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="21">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="23">
         <f>Parameters!C17</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="23">
         <f>Parameters!D15</f>
         <v>1.139</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="29">
         <f t="shared" si="0"/>
         <v>1068.8063099999999</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="29">
         <f t="shared" si="1"/>
         <v>1039.15526</v>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="25">
         <f t="shared" si="2"/>
         <v>0.50703310971651161</v>
       </c>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="21">
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="22">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="22">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="24">
         <f>Parameters!C17</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="24">
         <f>Parameters!D16</f>
         <v>0.93</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <f t="shared" si="0"/>
         <v>1068.8063099999999</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="31">
         <f t="shared" si="1"/>
         <v>848.47620000000006</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="26">
         <f t="shared" si="2"/>
         <v>0.55745895788722333</v>
       </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="20">
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="21">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="21">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="23">
         <f>Parameters!C17</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="23">
         <f>Parameters!D17</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <f t="shared" si="0"/>
         <v>1068.8063099999999</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <f t="shared" si="1"/>
         <v>712.53754000000004</v>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="25">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B11:H11"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/docs/brake_balance.xlsx
+++ b/docs/brake_balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF95BFD3-9C65-43E6-BE3C-A10A9BAA71E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92795D73-442E-496F-AAC6-6848CF21D631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -694,98 +694,98 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="20" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="23" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="24" fillId="24" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="25" fillId="25" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="26" fillId="26" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="27" fillId="27" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="24" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="25" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="25" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="20" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="23" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="24" fillId="24" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="25" fillId="25" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="26" fillId="26" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="27" fillId="27" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="20" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="24" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="25" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="25" fillId="25" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1029,288 +1029,288 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="J3" s="2"/>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="1" t="s">
+      <c r="A5" s="1"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="2"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="1"/>
       <c r="H5" s="33" t="s">
         <v>1</v>
       </c>
       <c r="I5" s="33"/>
-      <c r="J5" s="2"/>
+      <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
+      <c r="A6" s="1"/>
       <c r="B6" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="1"/>
+      <c r="H6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="J6" s="2"/>
+      <c r="I6" s="4">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" ht="51.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
+      <c r="A7" s="1"/>
       <c r="B7" s="32"/>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f>Calculations!H13</f>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="E7" s="10">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E7" s="9">
         <f>Calculations!H14</f>
-        <v>0.64752700397953378</v>
-      </c>
-      <c r="F7" s="10">
+        <v>0.62843172694583427</v>
+      </c>
+      <c r="F7" s="9">
         <f>Calculations!H15</f>
-        <v>0.68628238602128944</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="7" t="s">
+        <v>0.66821087554620473</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="8">
-        <v>300</v>
-      </c>
-      <c r="J7" s="2"/>
+      <c r="I7" s="7">
+        <v>320</v>
+      </c>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" ht="51.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
+      <c r="A8" s="1"/>
       <c r="B8" s="32"/>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f>Calculations!H16</f>
-        <v>0.55051302288871351</v>
-      </c>
-      <c r="E8" s="10">
+        <v>0.52997700878382348</v>
+      </c>
+      <c r="E8" s="9">
         <f>Calculations!H17</f>
-        <v>0.6</v>
-      </c>
-      <c r="F8" s="10">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F8" s="9">
         <f>Calculations!H18</f>
-        <v>0.64108455882352944</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="4" t="s">
+        <v>0.62184408936847202</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="8">
-        <v>300</v>
-      </c>
-      <c r="J8" s="2"/>
+      <c r="I8" s="7">
+        <v>320</v>
+      </c>
+      <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" ht="51.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
+      <c r="A9" s="1"/>
       <c r="B9" s="32"/>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <f>Calculations!H19</f>
-        <v>0.50703310971651161</v>
-      </c>
-      <c r="E9" s="10">
+        <v>0.48636402679951896</v>
+      </c>
+      <c r="E9" s="9">
         <f>Calculations!H20</f>
-        <v>0.55745895788722333</v>
-      </c>
-      <c r="F9" s="10">
+        <v>0.53697337537637213</v>
+      </c>
+      <c r="F9" s="9">
         <f>Calculations!H21</f>
-        <v>0.6</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="7" t="s">
+        <v>0.57999999999999985</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="2"/>
+      <c r="I9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="4" t="s">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="2"/>
+      <c r="I10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="J11" s="2"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="13" t="s">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <v>0.3</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="13">
         <v>0.5</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="13">
         <v>0.7</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="G12" s="1"/>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="15" t="s">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="J13" s="2"/>
+      <c r="G13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="J14" s="2"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1389,20 +1389,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2"/>
+      <c r="A2" s="1"/>
       <c r="B2" s="34" t="s">
         <v>14</v>
       </c>
@@ -1413,328 +1413,328 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
       <c r="I2" s="35"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
+      <c r="A3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
+      <c r="A5" s="1"/>
       <c r="B5" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
       <c r="G5" s="33" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="16" t="s">
+      <c r="A6" s="1"/>
+      <c r="B6" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="16" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="17">
+      <c r="A7" s="1"/>
+      <c r="B7" s="16">
         <v>300</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="17">
         <v>3509</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>3509</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="4" t="s">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="27">
         <v>0.72</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="27">
         <v>0.72</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="20">
+      <c r="A8" s="1"/>
+      <c r="B8" s="19">
         <v>320</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="17">
         <v>3743</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>3743</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="7" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="27">
         <v>0.68</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="27">
         <v>0.68</v>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="17">
+      <c r="A9" s="1"/>
+      <c r="B9" s="16">
         <v>355</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="17">
         <v>4153</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>4153</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="4" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="27">
         <v>0.65</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="27">
         <v>0.65</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="20">
+      <c r="A10" s="1"/>
+      <c r="B10" s="19">
         <v>370</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="17">
         <v>4329</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>4329</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
+      <c r="A13" s="1"/>
       <c r="B13" s="33" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="33"/>
       <c r="D13" s="33"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="16" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
     </row>
     <row r="15" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="21">
+      <c r="A15" s="1"/>
+      <c r="B15" s="20">
         <v>17.8</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="18">
         <v>1.139</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="18">
         <v>1.139</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="22">
+      <c r="A16" s="1"/>
+      <c r="B16" s="21">
         <v>19.7</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="18">
         <v>0.93</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="18">
         <v>0.93</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
     </row>
     <row r="17" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="21">
+      <c r="A17" s="1"/>
+      <c r="B17" s="20">
         <v>21.5</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="18">
         <v>0.78100000000000003</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="18">
         <v>0.78100000000000003</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
     </row>
     <row r="18" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
     </row>
     <row r="19" spans="1:11" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
+      <c r="A19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
+      <c r="A20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
     </row>
     <row r="21" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
+      <c r="A21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
     </row>
     <row r="22" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
+      <c r="A22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
     </row>
     <row r="23" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
+      <c r="A23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
+      <c r="A24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
+      <c r="A25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
     </row>
     <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1769,19 +1769,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2"/>
+      <c r="A2" s="1"/>
       <c r="B2" s="34" t="s">
         <v>27</v>
       </c>
@@ -1791,130 +1791,130 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
+      <c r="A3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="1"/>
+      <c r="B5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="1"/>
+      <c r="B6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="28">
         <f>INDEX(Parameters!$C$7:$C$10,MATCH('Balance Map'!$I$7,Parameters!$B$7:$B$10,0))</f>
-        <v>3509</v>
-      </c>
-      <c r="D6" s="29">
+        <v>3743</v>
+      </c>
+      <c r="D6" s="28">
         <f>INDEX(Parameters!$D$7:$D$10,MATCH('Balance Map'!$I$8,Parameters!$B$7:$B$10,0))</f>
-        <v>3509</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+        <v>3743</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="7" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <f>INDEX(Parameters!$H$7:$H$9,MATCH('Balance Map'!$I$9,Parameters!$G$7:$G$9,0))</f>
-        <v>0.65</v>
-      </c>
-      <c r="D7" s="30">
+        <v>0.72</v>
+      </c>
+      <c r="D7" s="29">
         <f>INDEX(Parameters!$I$7:$I$9,MATCH('Balance Map'!$I$10,Parameters!$G$7:$G$9,0))</f>
-        <v>0.65</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+        <v>0.72</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="28">
         <f>C6*C7*'Balance Map'!$I$6</f>
-        <v>1368.51</v>
-      </c>
-      <c r="D8" s="29">
+        <v>1563.0767999999998</v>
+      </c>
+      <c r="D8" s="28">
         <f>D6*D7*(1-'Balance Map'!$I$6)</f>
-        <v>912.34</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+        <v>1131.8832000000002</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
+      <c r="A11" s="1"/>
       <c r="B11" s="33" t="s">
         <v>34</v>
       </c>
@@ -1924,379 +1924,379 @@
       <c r="F11" s="33"/>
       <c r="G11" s="33"/>
       <c r="H11" s="33"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="16" t="s">
+      <c r="A12" s="1"/>
+      <c r="B12" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="21">
+      <c r="A13" s="1"/>
+      <c r="B13" s="20">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="20">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="22">
         <f>Parameters!C15</f>
         <v>1.139</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="22">
         <f>Parameters!D15</f>
         <v>1.139</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="28">
         <f t="shared" ref="F13:F21" si="0">$C$8*D13</f>
-        <v>1558.73289</v>
-      </c>
-      <c r="G13" s="29">
+        <v>1780.3444751999998</v>
+      </c>
+      <c r="G13" s="28">
         <f t="shared" ref="G13:G21" si="1">$D$8*E13</f>
-        <v>1039.15526</v>
-      </c>
-      <c r="H13" s="25">
+        <v>1289.2149648000002</v>
+      </c>
+      <c r="H13" s="24">
         <f t="shared" ref="H13:H21" si="2">F13/(F13+G13)</f>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="22">
+      <c r="A14" s="1"/>
+      <c r="B14" s="21">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="21">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="23">
         <f>Parameters!C15</f>
         <v>1.139</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="23">
         <f>Parameters!D16</f>
         <v>0.93</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="30">
         <f t="shared" si="0"/>
-        <v>1558.73289</v>
-      </c>
-      <c r="G14" s="31">
+        <v>1780.3444751999998</v>
+      </c>
+      <c r="G14" s="30">
         <f t="shared" si="1"/>
-        <v>848.47620000000006</v>
-      </c>
-      <c r="H14" s="26">
+        <v>1052.6513760000003</v>
+      </c>
+      <c r="H14" s="25">
         <f t="shared" si="2"/>
-        <v>0.64752700397953378</v>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
+        <v>0.62843172694583427</v>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="21">
+      <c r="A15" s="1"/>
+      <c r="B15" s="20">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="20">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="22">
         <f>Parameters!C15</f>
         <v>1.139</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="22">
         <f>Parameters!D17</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="28">
         <f t="shared" si="0"/>
-        <v>1558.73289</v>
-      </c>
-      <c r="G15" s="29">
+        <v>1780.3444751999998</v>
+      </c>
+      <c r="G15" s="28">
         <f t="shared" si="1"/>
-        <v>712.53754000000004</v>
-      </c>
-      <c r="H15" s="25">
+        <v>884.00077920000024</v>
+      </c>
+      <c r="H15" s="24">
         <f t="shared" si="2"/>
-        <v>0.68628238602128944</v>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+        <v>0.66821087554620473</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="22">
+      <c r="A16" s="1"/>
+      <c r="B16" s="21">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="21">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="23">
         <f>Parameters!C16</f>
         <v>0.93</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="23">
         <f>Parameters!D15</f>
         <v>1.139</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <f t="shared" si="0"/>
-        <v>1272.7143000000001</v>
-      </c>
-      <c r="G16" s="31">
+        <v>1453.6614239999999</v>
+      </c>
+      <c r="G16" s="30">
         <f t="shared" si="1"/>
-        <v>1039.15526</v>
-      </c>
-      <c r="H16" s="26">
+        <v>1289.2149648000002</v>
+      </c>
+      <c r="H16" s="25">
         <f t="shared" si="2"/>
-        <v>0.55051302288871351</v>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+        <v>0.52997700878382348</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="21">
+      <c r="A17" s="1"/>
+      <c r="B17" s="20">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="22">
         <f>Parameters!C16</f>
         <v>0.93</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="22">
         <f>Parameters!D16</f>
         <v>0.93</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="28">
         <f t="shared" si="0"/>
-        <v>1272.7143000000001</v>
-      </c>
-      <c r="G17" s="29">
+        <v>1453.6614239999999</v>
+      </c>
+      <c r="G17" s="28">
         <f t="shared" si="1"/>
-        <v>848.47620000000006</v>
-      </c>
-      <c r="H17" s="25">
+        <v>1052.6513760000003</v>
+      </c>
+      <c r="H17" s="24">
         <f t="shared" si="2"/>
-        <v>0.6</v>
-      </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="22">
+      <c r="A18" s="1"/>
+      <c r="B18" s="21">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="21">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="23">
         <f>Parameters!C16</f>
         <v>0.93</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="23">
         <f>Parameters!D17</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="30">
         <f t="shared" si="0"/>
-        <v>1272.7143000000001</v>
-      </c>
-      <c r="G18" s="31">
+        <v>1453.6614239999999</v>
+      </c>
+      <c r="G18" s="30">
         <f t="shared" si="1"/>
-        <v>712.53754000000004</v>
-      </c>
-      <c r="H18" s="26">
+        <v>884.00077920000024</v>
+      </c>
+      <c r="H18" s="25">
         <f t="shared" si="2"/>
-        <v>0.64108455882352944</v>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+        <v>0.62184408936847202</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="21">
+      <c r="A19" s="1"/>
+      <c r="B19" s="20">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="20">
         <f>Parameters!B15</f>
         <v>17.8</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="22">
         <f>Parameters!C17</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="22">
         <f>Parameters!D15</f>
         <v>1.139</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="28">
         <f t="shared" si="0"/>
-        <v>1068.8063099999999</v>
-      </c>
-      <c r="G19" s="29">
+        <v>1220.7629807999999</v>
+      </c>
+      <c r="G19" s="28">
         <f t="shared" si="1"/>
-        <v>1039.15526</v>
-      </c>
-      <c r="H19" s="25">
+        <v>1289.2149648000002</v>
+      </c>
+      <c r="H19" s="24">
         <f t="shared" si="2"/>
-        <v>0.50703310971651161</v>
-      </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+        <v>0.48636402679951896</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="22">
+      <c r="A20" s="1"/>
+      <c r="B20" s="21">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="21">
         <f>Parameters!B16</f>
         <v>19.7</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="23">
         <f>Parameters!C17</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="23">
         <f>Parameters!D16</f>
         <v>0.93</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="30">
         <f t="shared" si="0"/>
-        <v>1068.8063099999999</v>
-      </c>
-      <c r="G20" s="31">
+        <v>1220.7629807999999</v>
+      </c>
+      <c r="G20" s="30">
         <f t="shared" si="1"/>
-        <v>848.47620000000006</v>
-      </c>
-      <c r="H20" s="26">
+        <v>1052.6513760000003</v>
+      </c>
+      <c r="H20" s="25">
         <f t="shared" si="2"/>
-        <v>0.55745895788722333</v>
-      </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+        <v>0.53697337537637213</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="21">
+      <c r="A21" s="1"/>
+      <c r="B21" s="20">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="20">
         <f>Parameters!B17</f>
         <v>21.5</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="22">
         <f>Parameters!C17</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="22">
         <f>Parameters!D17</f>
         <v>0.78100000000000003</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="28">
         <f t="shared" si="0"/>
-        <v>1068.8063099999999</v>
-      </c>
-      <c r="G21" s="29">
+        <v>1220.7629807999999</v>
+      </c>
+      <c r="G21" s="28">
         <f t="shared" si="1"/>
-        <v>712.53754000000004</v>
-      </c>
-      <c r="H21" s="25">
+        <v>884.00077920000024</v>
+      </c>
+      <c r="H21" s="24">
         <f t="shared" si="2"/>
-        <v>0.6</v>
-      </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+        <v>0.57999999999999985</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/brake_balance.xlsx
+++ b/docs/brake_balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92795D73-442E-496F-AAC6-6848CF21D631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A852C5EE-63C2-49DF-B3BA-91097CD555EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1108,7 +1108,7 @@
         <v>3</v>
       </c>
       <c r="I6" s="4">
-        <v>0.57999999999999996</v>
+        <v>0.62</v>
       </c>
       <c r="J6" s="1"/>
     </row>
@@ -1121,15 +1121,15 @@
       </c>
       <c r="D7" s="9">
         <f>Calculations!H13</f>
-        <v>0.57999999999999996</v>
+        <v>0.62</v>
       </c>
       <c r="E7" s="9">
         <f>Calculations!H14</f>
-        <v>0.62843172694583427</v>
+        <v>0.66647162083089517</v>
       </c>
       <c r="F7" s="9">
         <f>Calculations!H15</f>
-        <v>0.66821087554620473</v>
+        <v>0.70409587620642899</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="6" t="s">
@@ -1149,15 +1149,15 @@
       </c>
       <c r="D8" s="9">
         <f>Calculations!H16</f>
-        <v>0.52997700878382348</v>
+        <v>0.5712191159279586</v>
       </c>
       <c r="E8" s="9">
         <f>Calculations!H17</f>
-        <v>0.57999999999999996</v>
+        <v>0.61999999999999988</v>
       </c>
       <c r="F8" s="9">
         <f>Calculations!H18</f>
-        <v>0.62184408936847202</v>
+        <v>0.66019373010602489</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="3" t="s">
@@ -1177,15 +1177,15 @@
       </c>
       <c r="D9" s="9">
         <f>Calculations!H19</f>
-        <v>0.48636402679951896</v>
+        <v>0.52802494983861115</v>
       </c>
       <c r="E9" s="9">
         <f>Calculations!H20</f>
-        <v>0.53697337537637213</v>
+        <v>0.57809030347890455</v>
       </c>
       <c r="F9" s="9">
         <f>Calculations!H21</f>
-        <v>0.57999999999999985</v>
+        <v>0.61999999999999988</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="6" t="s">
@@ -1876,11 +1876,11 @@
       </c>
       <c r="C8" s="28">
         <f>C6*C7*'Balance Map'!$I$6</f>
-        <v>1563.0767999999998</v>
+        <v>1670.8751999999999</v>
       </c>
       <c r="D8" s="28">
         <f>D6*D7*(1-'Balance Map'!$I$6)</f>
-        <v>1131.8832000000002</v>
+        <v>1024.0848000000001</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -1973,15 +1973,15 @@
       </c>
       <c r="F13" s="28">
         <f t="shared" ref="F13:F21" si="0">$C$8*D13</f>
-        <v>1780.3444751999998</v>
+        <v>1903.1268528000001</v>
       </c>
       <c r="G13" s="28">
         <f t="shared" ref="G13:G21" si="1">$D$8*E13</f>
-        <v>1289.2149648000002</v>
+        <v>1166.4325872000002</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" ref="H13:H21" si="2">F13/(F13+G13)</f>
-        <v>0.57999999999999996</v>
+        <v>0.62</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -2006,15 +2006,15 @@
       </c>
       <c r="F14" s="30">
         <f t="shared" si="0"/>
-        <v>1780.3444751999998</v>
+        <v>1903.1268528000001</v>
       </c>
       <c r="G14" s="30">
         <f t="shared" si="1"/>
-        <v>1052.6513760000003</v>
+        <v>952.39886400000012</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="2"/>
-        <v>0.62843172694583427</v>
+        <v>0.66647162083089517</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -2039,15 +2039,15 @@
       </c>
       <c r="F15" s="28">
         <f t="shared" si="0"/>
-        <v>1780.3444751999998</v>
+        <v>1903.1268528000001</v>
       </c>
       <c r="G15" s="28">
         <f t="shared" si="1"/>
-        <v>884.00077920000024</v>
+        <v>799.81022880000012</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="2"/>
-        <v>0.66821087554620473</v>
+        <v>0.70409587620642899</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -2072,15 +2072,15 @@
       </c>
       <c r="F16" s="30">
         <f t="shared" si="0"/>
-        <v>1453.6614239999999</v>
+        <v>1553.9139359999999</v>
       </c>
       <c r="G16" s="30">
         <f t="shared" si="1"/>
-        <v>1289.2149648000002</v>
+        <v>1166.4325872000002</v>
       </c>
       <c r="H16" s="25">
         <f t="shared" si="2"/>
-        <v>0.52997700878382348</v>
+        <v>0.5712191159279586</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -2105,15 +2105,15 @@
       </c>
       <c r="F17" s="28">
         <f t="shared" si="0"/>
-        <v>1453.6614239999999</v>
+        <v>1553.9139359999999</v>
       </c>
       <c r="G17" s="28">
         <f t="shared" si="1"/>
-        <v>1052.6513760000003</v>
+        <v>952.39886400000012</v>
       </c>
       <c r="H17" s="24">
         <f t="shared" si="2"/>
-        <v>0.57999999999999996</v>
+        <v>0.61999999999999988</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -2138,15 +2138,15 @@
       </c>
       <c r="F18" s="30">
         <f t="shared" si="0"/>
-        <v>1453.6614239999999</v>
+        <v>1553.9139359999999</v>
       </c>
       <c r="G18" s="30">
         <f t="shared" si="1"/>
-        <v>884.00077920000024</v>
+        <v>799.81022880000012</v>
       </c>
       <c r="H18" s="25">
         <f t="shared" si="2"/>
-        <v>0.62184408936847202</v>
+        <v>0.66019373010602489</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -2171,15 +2171,15 @@
       </c>
       <c r="F19" s="28">
         <f t="shared" si="0"/>
-        <v>1220.7629807999999</v>
+        <v>1304.9535312</v>
       </c>
       <c r="G19" s="28">
         <f t="shared" si="1"/>
-        <v>1289.2149648000002</v>
+        <v>1166.4325872000002</v>
       </c>
       <c r="H19" s="24">
         <f t="shared" si="2"/>
-        <v>0.48636402679951896</v>
+        <v>0.52802494983861115</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -2204,15 +2204,15 @@
       </c>
       <c r="F20" s="30">
         <f t="shared" si="0"/>
-        <v>1220.7629807999999</v>
+        <v>1304.9535312</v>
       </c>
       <c r="G20" s="30">
         <f t="shared" si="1"/>
-        <v>1052.6513760000003</v>
+        <v>952.39886400000012</v>
       </c>
       <c r="H20" s="25">
         <f t="shared" si="2"/>
-        <v>0.53697337537637213</v>
+        <v>0.57809030347890455</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -2237,15 +2237,15 @@
       </c>
       <c r="F21" s="28">
         <f t="shared" si="0"/>
-        <v>1220.7629807999999</v>
+        <v>1304.9535312</v>
       </c>
       <c r="G21" s="28">
         <f t="shared" si="1"/>
-        <v>884.00077920000024</v>
+        <v>799.81022880000012</v>
       </c>
       <c r="H21" s="24">
         <f t="shared" si="2"/>
-        <v>0.57999999999999985</v>
+        <v>0.61999999999999988</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>

--- a/docs/brake_balance.xlsx
+++ b/docs/brake_balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A852C5EE-63C2-49DF-B3BA-91097CD555EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CB661C-89CD-4428-B824-F292DBEA9A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/docs/brake_balance.xlsx
+++ b/docs/brake_balance.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\xlsx-locale-20261027\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CB661C-89CD-4428-B824-F292DBEA9A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AC3E66-BF99-4FD5-A577-E247D35DA850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Balance Map" sheetId="1" r:id="rId1"/>
     <sheet name="Parameters" sheetId="2" r:id="rId2"/>
     <sheet name="Calculations" sheetId="3" r:id="rId3"/>
+    <sheet name="Locale" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="127">
   <si>
     <t>Astral · Brake balance</t>
   </si>
@@ -161,6 +162,263 @@
   </si>
   <si>
     <t>Front share</t>
+  </si>
+  <si>
+    <t>Language / 语言</t>
+  </si>
+  <si>
+    <t>简体中文</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>en-US</t>
+  </si>
+  <si>
+    <t>zh-CN</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>label.balanceBar</t>
+  </si>
+  <si>
+    <t>制动平衡杆</t>
+  </si>
+  <si>
+    <t>label.brakeDiscConstants</t>
+  </si>
+  <si>
+    <t>制动盘常数</t>
+  </si>
+  <si>
+    <t>label.brakePadMultipliers</t>
+  </si>
+  <si>
+    <t>制动片倍率</t>
+  </si>
+  <si>
+    <t>label.discMm</t>
+  </si>
+  <si>
+    <t>制动盘 (mm)</t>
+  </si>
+  <si>
+    <t>label.discTorqueConstant</t>
+  </si>
+  <si>
+    <t>制动盘 K (N·m)</t>
+  </si>
+  <si>
+    <t>label.equalFrontRear</t>
+  </si>
+  <si>
+    <t>Equal front / rear</t>
+  </si>
+  <si>
+    <t>label.fixedColorScale</t>
+  </si>
+  <si>
+    <t>Fixed color scale</t>
+  </si>
+  <si>
+    <t>label.front</t>
+  </si>
+  <si>
+    <t>前轴</t>
+  </si>
+  <si>
+    <t>label.frontBiased</t>
+  </si>
+  <si>
+    <t>Front-biased</t>
+  </si>
+  <si>
+    <t>label.frontDisc</t>
+  </si>
+  <si>
+    <t>前轴制动盘</t>
+  </si>
+  <si>
+    <t>label.frontMasterCylinder</t>
+  </si>
+  <si>
+    <t>前制动主缸</t>
+  </si>
+  <si>
+    <t>label.frontMasterCylinderMm</t>
+  </si>
+  <si>
+    <t>前制动主缸 (mm)</t>
+  </si>
+  <si>
+    <t>label.frontMasterCylinderMultiplier</t>
+  </si>
+  <si>
+    <t>前制动主缸 ×</t>
+  </si>
+  <si>
+    <t>label.frontMultiplier</t>
+  </si>
+  <si>
+    <t>前轴 ×</t>
+  </si>
+  <si>
+    <t>label.frontPad</t>
+  </si>
+  <si>
+    <t>前轴制动片</t>
+  </si>
+  <si>
+    <t>label.frontShare</t>
+  </si>
+  <si>
+    <t>前轴占比</t>
+  </si>
+  <si>
+    <t>label.frontTorqueConstant</t>
+  </si>
+  <si>
+    <t>前轴 K (N·m)</t>
+  </si>
+  <si>
+    <t>label.frontWeight</t>
+  </si>
+  <si>
+    <t>前轴权重</t>
+  </si>
+  <si>
+    <t>label.masterCylinderCombinations</t>
+  </si>
+  <si>
+    <t>制动主缸组合</t>
+  </si>
+  <si>
+    <t>label.masterCylinderMm</t>
+  </si>
+  <si>
+    <t>制动主缸 (mm)</t>
+  </si>
+  <si>
+    <t>label.masterCylinderMultipliers</t>
+  </si>
+  <si>
+    <t>制动主缸倍率</t>
+  </si>
+  <si>
+    <t>label.pad</t>
+  </si>
+  <si>
+    <t>制动片</t>
+  </si>
+  <si>
+    <t>label.padMultiplier</t>
+  </si>
+  <si>
+    <t>label.rear</t>
+  </si>
+  <si>
+    <t>后轴</t>
+  </si>
+  <si>
+    <t>label.rearBiased</t>
+  </si>
+  <si>
+    <t>Rear-biased</t>
+  </si>
+  <si>
+    <t>label.rearBrakeK</t>
+  </si>
+  <si>
+    <t>后轴 K (N·m)</t>
+  </si>
+  <si>
+    <t>label.rearDisc</t>
+  </si>
+  <si>
+    <t>后轴制动盘</t>
+  </si>
+  <si>
+    <t>label.rearFactor</t>
+  </si>
+  <si>
+    <t>后轴 ×</t>
+  </si>
+  <si>
+    <t>label.rearMasterCylinder</t>
+  </si>
+  <si>
+    <t>后制动主缸</t>
+  </si>
+  <si>
+    <t>label.rearMasterCylinderFactor</t>
+  </si>
+  <si>
+    <t>后制动主缸 ×</t>
+  </si>
+  <si>
+    <t>label.rearMasterCylinderMm</t>
+  </si>
+  <si>
+    <t>后制动主缸 (mm)</t>
+  </si>
+  <si>
+    <t>label.rearPad</t>
+  </si>
+  <si>
+    <t>后轴制动片</t>
+  </si>
+  <si>
+    <t>label.rearWeight</t>
+  </si>
+  <si>
+    <t>后轴权重</t>
+  </si>
+  <si>
+    <t>label.selectedSetup</t>
+  </si>
+  <si>
+    <t>所选设定</t>
+  </si>
+  <si>
+    <t>label.setup</t>
+  </si>
+  <si>
+    <t>设定组合</t>
+  </si>
+  <si>
+    <t>label.weightBeforeMasterCylinder</t>
+  </si>
+  <si>
+    <t>主缸前权重</t>
+  </si>
+  <si>
+    <t>title.brakeBalance</t>
+  </si>
+  <si>
+    <t>Astral · 制动平衡</t>
+  </si>
+  <si>
+    <t>title.brakeCalculations</t>
+  </si>
+  <si>
+    <t>Astral · 制动计算</t>
+  </si>
+  <si>
+    <t>title.brakeParameters</t>
+  </si>
+  <si>
+    <t>Astral · 制动参数</t>
+  </si>
+  <si>
+    <t>Type-A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>简体中文</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -173,7 +431,7 @@
     <numFmt numFmtId="178" formatCode="0&quot; mm&quot;"/>
     <numFmt numFmtId="179" formatCode="0.000"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,8 +606,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,8 +757,21 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -684,13 +968,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -784,6 +1075,8 @@
     <xf numFmtId="1" fontId="25" fillId="25" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -793,6 +1086,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -801,7 +1100,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1015,35 +1314,48 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.125" customWidth="1"/>
-    <col min="3" max="6" width="17.625" customWidth="1"/>
+    <col min="2" max="2" width="12.08203125" customWidth="1"/>
+    <col min="3" max="6" width="17.58203125" customWidth="1"/>
     <col min="7" max="7" width="4" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="3" customWidth="1"/>
-    <col min="11" max="11" width="29.125" customWidth="1"/>
+    <col min="11" max="11" width="29.08203125" customWidth="1"/>
     <col min="12" max="12" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>43</v>
+      </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="35.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
-        <v>0</v>
+      <c r="B2" s="2" t="str">
+        <f>VLOOKUP("title.brakeBalance",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>Astral · 制动平衡</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1053,12 +1365,12 @@
       <c r="H2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1070,26 +1382,29 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="26"/>
-      <c r="C5" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
+      <c r="C5" s="33" t="str">
+        <f>VLOOKUP("label.rearMasterCylinder",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>后制动主缸</v>
+      </c>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="33"/>
+      <c r="H5" s="35" t="str">
+        <f>VLOOKUP("label.setup",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>设定组合</v>
+      </c>
+      <c r="I5" s="35"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="32" t="s">
-        <v>4</v>
+      <c r="B6" s="34" t="str">
+        <f>VLOOKUP("label.frontMasterCylinder",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>前制动主缸</v>
       </c>
       <c r="D6" s="8">
         <f>Parameters!B15</f>
@@ -1104,17 +1419,18 @@
         <v>21.5</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6" s="3" t="s">
-        <v>3</v>
+      <c r="H6" s="3" t="str">
+        <f>VLOOKUP("label.balanceBar",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>制动平衡杆</v>
       </c>
       <c r="I6" s="4">
         <v>0.62</v>
       </c>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="51.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="32"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="8">
         <f>Parameters!B15</f>
         <v>17.8</v>
@@ -1132,17 +1448,18 @@
         <v>0.70409587620642899</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="6" t="s">
-        <v>5</v>
+      <c r="H7" s="6" t="str">
+        <f>VLOOKUP("label.frontDisc",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>前轴制动盘</v>
       </c>
       <c r="I7" s="7">
         <v>320</v>
       </c>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="51.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="32"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="10">
         <f>Parameters!B16</f>
         <v>19.7</v>
@@ -1160,17 +1477,18 @@
         <v>0.66019373010602489</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8" s="3" t="s">
-        <v>6</v>
+      <c r="H8" s="3" t="str">
+        <f>VLOOKUP("label.rearDisc",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>后轴制动盘</v>
       </c>
       <c r="I8" s="7">
         <v>320</v>
       </c>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="51.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="32"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="8">
         <f>Parameters!B17</f>
         <v>21.5</v>
@@ -1188,15 +1506,16 @@
         <v>0.61999999999999988</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="6" t="s">
-        <v>7</v>
+      <c r="H9" s="6" t="str">
+        <f>VLOOKUP("label.frontPad",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>前轴制动片</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1204,15 +1523,16 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="3" t="s">
-        <v>9</v>
+      <c r="H10" s="3" t="str">
+        <f>VLOOKUP("label.rearPad",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>后轴制动片</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1222,11 +1542,12 @@
       <c r="G11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="12" t="s">
-        <v>10</v>
+      <c r="C12" s="12" t="str">
+        <f>VLOOKUP("label.fixedColorScale",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>固定色阶</v>
       </c>
       <c r="D12" s="13">
         <v>0.3</v>
@@ -1240,23 +1561,26 @@
       <c r="G12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>13</v>
+      <c r="D13" s="14" t="str">
+        <f>VLOOKUP("label.rearBiased",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>偏后</v>
+      </c>
+      <c r="E13" s="14" t="str">
+        <f>VLOOKUP("label.equalFrontRear",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>前后相等</v>
+      </c>
+      <c r="F13" s="14" t="str">
+        <f>VLOOKUP("label.frontBiased",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>偏前</v>
       </c>
       <c r="G13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1266,17 +1590,17 @@
       <c r="G14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1288,7 +1612,7 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1300,7 +1624,7 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1313,10 +1637,12 @@
       <c r="J19" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D7:F9">
@@ -1343,13 +1669,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="decimal" sqref="I6" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0.4</formula1>
       <formula2>0.6</formula2>
     </dataValidation>
+    <dataValidation type="list" sqref="E1:G1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"English,简体中文"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -1377,7 +1707,7 @@
     <tabColor rgb="FFC49A32"/>
   </sheetPr>
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1388,7 +1718,7 @@
     <col min="10" max="11" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1401,27 +1731,28 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="35.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
+      <c r="B2" s="38" t="str">
+        <f>VLOOKUP("title.brakeParameters",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>Astral · 制动参数</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1434,49 +1765,57 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
+      <c r="B5" s="35" t="str">
+        <f>VLOOKUP("label.brakeDiscConstants",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>制动盘常数</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
+      <c r="G5" s="35" t="str">
+        <f>VLOOKUP("label.brakePadMultipliers",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>制动片倍率</v>
+      </c>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>19</v>
+      <c r="B6" s="15" t="str">
+        <f>VLOOKUP("label.discMm",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>制动盘 (mm)</v>
+      </c>
+      <c r="C6" s="15" t="str">
+        <f>VLOOKUP("label.frontTorqueConstant",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>前轴 K (N·m)</v>
+      </c>
+      <c r="D6" s="15" t="str">
+        <f>VLOOKUP("label.rearBrakeK",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>后轴 K (N·m)</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>22</v>
+      <c r="G6" s="15" t="str">
+        <f>VLOOKUP("label.pad",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>制动片</v>
+      </c>
+      <c r="H6" s="15" t="str">
+        <f>VLOOKUP("label.frontMultiplier",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>前轴 ×</v>
+      </c>
+      <c r="I6" s="15" t="str">
+        <f>VLOOKUP("label.rearFactor",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>后轴 ×</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="16">
         <v>300</v>
@@ -1501,7 +1840,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="19">
         <v>320</v>
@@ -1526,7 +1865,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="16">
         <v>355</v>
@@ -1551,7 +1890,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="19">
         <v>370</v>
@@ -1570,7 +1909,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1583,7 +1922,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1593,35 +1932,39 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
+      <c r="B13" s="35" t="str">
+        <f>VLOOKUP("label.masterCylinderMultipliers",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>制动主缸倍率</v>
+      </c>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>22</v>
+      <c r="B14" s="15" t="str">
+        <f>VLOOKUP("label.masterCylinderMm",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>制动主缸 (mm)</v>
+      </c>
+      <c r="C14" s="15" t="str">
+        <f>VLOOKUP("label.frontMultiplier",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>前轴 ×</v>
+      </c>
+      <c r="D14" s="15" t="str">
+        <f>VLOOKUP("label.rearFactor",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>后轴 ×</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="20">
         <v>17.8</v>
@@ -1637,7 +1980,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="21">
         <v>19.7</v>
@@ -1656,7 +1999,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="20">
         <v>21.5</v>
@@ -1675,7 +2018,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1688,42 +2031,42 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
-    <row r="25" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
     </row>
-    <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1750,6 +2093,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1759,7 +2103,7 @@
     <tabColor rgb="FF93A0AC"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -1768,7 +2112,7 @@
     <col min="9" max="10" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1780,26 +2124,27 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="35.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="38" t="str">
+        <f>VLOOKUP("title.brakeCalculations",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>Astral · 制动计算</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1811,16 +2156,19 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>30</v>
+      <c r="B5" s="5" t="str">
+        <f>VLOOKUP("label.selectedSetup",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>所选设定</v>
+      </c>
+      <c r="C5" s="5" t="str">
+        <f>VLOOKUP("label.front",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>前轴</v>
+      </c>
+      <c r="D5" s="5" t="str">
+        <f>VLOOKUP("label.rear",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>后轴</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1829,10 +2177,11 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="3" t="s">
-        <v>31</v>
+      <c r="B6" s="3" t="str">
+        <f>VLOOKUP("label.discTorqueConstant",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>制动盘 K (N·m)</v>
       </c>
       <c r="C6" s="28">
         <f>INDEX(Parameters!$C$7:$C$10,MATCH('Balance Map'!$I$7,Parameters!$B$7:$B$10,0))</f>
@@ -1849,10 +2198,11 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="6" t="s">
-        <v>32</v>
+      <c r="B7" s="6" t="str">
+        <f>VLOOKUP("label.padMultiplier",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>制动片倍率</v>
       </c>
       <c r="C7" s="29">
         <f>INDEX(Parameters!$H$7:$H$9,MATCH('Balance Map'!$I$9,Parameters!$G$7:$G$9,0))</f>
@@ -1869,10 +2219,11 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="3" t="s">
-        <v>33</v>
+      <c r="B8" s="3" t="str">
+        <f>VLOOKUP("label.weightBeforeMasterCylinder",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>主缸前权重</v>
       </c>
       <c r="C8" s="28">
         <f>C6*C7*'Balance Map'!$I$6</f>
@@ -1889,7 +2240,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1901,7 +2252,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1913,47 +2264,55 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
+      <c r="B11" s="35" t="str">
+        <f>VLOOKUP("label.masterCylinderCombinations",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>制动主缸组合</v>
+      </c>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>41</v>
+      <c r="B12" s="15" t="str">
+        <f>VLOOKUP("label.frontMasterCylinderMm",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>前制动主缸 (mm)</v>
+      </c>
+      <c r="C12" s="15" t="str">
+        <f>VLOOKUP("label.rearMasterCylinderMm",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>后制动主缸 (mm)</v>
+      </c>
+      <c r="D12" s="15" t="str">
+        <f>VLOOKUP("label.frontMasterCylinderMultiplier",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>前制动主缸 ×</v>
+      </c>
+      <c r="E12" s="15" t="str">
+        <f>VLOOKUP("label.rearMasterCylinderFactor",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>后制动主缸 ×</v>
+      </c>
+      <c r="F12" s="15" t="str">
+        <f>VLOOKUP("label.frontWeight",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>前轴权重</v>
+      </c>
+      <c r="G12" s="15" t="str">
+        <f>VLOOKUP("label.rearWeight",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>后轴权重</v>
+      </c>
+      <c r="H12" s="15" t="str">
+        <f>VLOOKUP("label.frontShare",Locale!$A$2:$D$40,4,FALSE)</f>
+        <v>前轴占比</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="20">
         <f>Parameters!B15</f>
@@ -1986,7 +2345,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="21">
         <f>Parameters!B15</f>
@@ -2019,7 +2378,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="20">
         <f>Parameters!B15</f>
@@ -2052,7 +2411,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="21">
         <f>Parameters!B16</f>
@@ -2085,7 +2444,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="20">
         <f>Parameters!B16</f>
@@ -2118,7 +2477,7 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="21">
         <f>Parameters!B16</f>
@@ -2151,7 +2510,7 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="20">
         <f>Parameters!B17</f>
@@ -2184,7 +2543,7 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="21">
         <f>Parameters!B17</f>
@@ -2217,7 +2576,7 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="20">
         <f>Parameters!B17</f>
@@ -2250,7 +2609,7 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2262,7 +2621,7 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2274,7 +2633,7 @@
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2286,7 +2645,7 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2307,4 +2666,614 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D40"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B2,C2)</f>
+        <v>制动平衡杆</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B3,C3)</f>
+        <v>制动盘常数</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B4,C4)</f>
+        <v>制动片倍率</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B5,C5)</f>
+        <v>制动盘 (mm)</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B6,C6)</f>
+        <v>制动盘 K (N·m)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B7,C7)</f>
+        <v>前后相等</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B8,C8)</f>
+        <v>固定色阶</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B9,C9)</f>
+        <v>前轴</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B10,C10)</f>
+        <v>偏前</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B11,C11)</f>
+        <v>前轴制动盘</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B12,C12)</f>
+        <v>前制动主缸</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B13,C13)</f>
+        <v>前制动主缸 (mm)</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B14,C14)</f>
+        <v>前制动主缸 ×</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B15,C15)</f>
+        <v>前轴 ×</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B16,C16)</f>
+        <v>前轴制动片</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B17,C17)</f>
+        <v>前轴占比</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B18,C18)</f>
+        <v>前轴 K (N·m)</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B19,C19)</f>
+        <v>前轴权重</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B20,C20)</f>
+        <v>制动主缸组合</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B21,C21)</f>
+        <v>制动主缸 (mm)</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B22,C22)</f>
+        <v>制动主缸倍率</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B23,C23)</f>
+        <v>制动片</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B24,C24)</f>
+        <v>制动片倍率</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B25,C25)</f>
+        <v>后轴</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B26,C26)</f>
+        <v>偏后</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B27,C27)</f>
+        <v>后轴 K (N·m)</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B28,C28)</f>
+        <v>后轴制动盘</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B29,C29)</f>
+        <v>后轴 ×</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B30,C30)</f>
+        <v>后制动主缸</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B31,C31)</f>
+        <v>后制动主缸 ×</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B32,C32)</f>
+        <v>后制动主缸 (mm)</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B33,C33)</f>
+        <v>后轴制动片</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B34,C34)</f>
+        <v>后轴权重</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B35,C35)</f>
+        <v>所选设定</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B36,C36)</f>
+        <v>设定组合</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B37,C37)</f>
+        <v>主缸前权重</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B38,C38)</f>
+        <v>Astral · 制动平衡</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B39,C39)</f>
+        <v>Astral · 制动计算</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" s="31" t="str">
+        <f>IF('Balance Map'!$E$1="English",B40,C40)</f>
+        <v>Astral · 制动参数</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>